--- a/datasets/general_data_dataset_booking.xlsx
+++ b/datasets/general_data_dataset_booking.xlsx
@@ -425,38 +425,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>camping_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>camping_address</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>camping_description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>camping_host_description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>camping_facilities</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>url</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>camping_name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>camping_address</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>camping_description</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>camping_host_description</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>camping_facilities</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -466,20 +471,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-tre-archi.it.html</t>
+          <t>CAMPING TRE ARCHI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CAMPING TRE ARCHI</t>
+          <t>via ugo la malfa 19/A, 63900 Lido di Fermo, Italia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>via ugo la malfa 19/A, 63900 Lido di Fermo, Italia</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>Hai diritto a uno sconto Genius su CAMPING TRE ARCHI! Per risparmiare su questa struttura ti basta accedere.
 Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Situato a Lido di Fermo, a 25 km da Porto Recanati, il CAMPING TRE ARCHI offre un ristorante e il WiFi gratuito.
@@ -490,7 +490,7 @@
 La struttura dista 36 km da Sirolo e 39 km da San Benedetto del Tronto. Il CAMPING TRE ARCHI si trova a 63 km dall’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>I  bungalow si trovano sulla riviera fermana,direttamente sulla spiaggia,lontano dalla ferrovia o strade rumorosee immerso nel verde pioppeto del camping Tre Archi.l trilocali sono di nuova costruzione dotato di tutti i confort  e hanno il posto auto privato davanti alla struttura.Il posto è adatto alla famiglia con figli per la presenza di parco giochi,campo di pallone,pallacanestro,bocce,ping pong,animazione serale,miniclub per bambini ,aria condizionata,barbecue,nessuna strada d'attraversare per la spiaggia,possibilità di affittare biciclette ed attrezzatura da spiaggia.wi-fi gratuito.
 Adiacente alla struttura passa una lunga pista ciclabile che unisce Porto San Giorgio e Porto Sant' Elpidio.Nelle vicinanze: piscina,supermarket,ristoranti,pizzerie,stabilimenti attrezzati,
@@ -498,7 +498,7 @@
 :</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Arredamento da esterni, Barbecue, Barbecue, Terrazza, Giardino, | CUCINA: Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Escursioni in bicicletta
 Non sul posto, Escursionismo
@@ -509,6 +509,16 @@
 a pagamento, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Rumeno, | </t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-tre-archi.it.html</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>camping-tre-archi</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -516,20 +526,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-village-mar-y-sierra.it.html</t>
+          <t>Camping Village Mar y Sierra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Camping Village Mar y Sierra</t>
+          <t>Strada San Gervasio 3, 61039 San Costanzo, Italia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>Strada San Gervasio 3, 61039 San Costanzo, Italia</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>Situato a San Costanzo, il Camping Village Mar y Sierra vanta una piscina all'aperto, la connessione WiFi gratuita nelle aree comuni e camere climatizzate, in alcuni casi con terrazza.
 Ciascuna sistemazione presenta anche una TV a schermo piatto, una scrivania e un bagno privato con set di cortesia.
@@ -537,12 +542,12 @@
 Completo di parcheggio gratuito, il Camping Village Mar y Sierra dista, in auto, 10 minuti dalle spiagge della zona e 40 minuti da Pesaro.</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Terrazza solarium, Barbecue, Terrazza, Giardino, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Spiaggia, Armadietti per fitness/spa, Attrezzatura da tennis, Parco acquatico
 Non sul posto
@@ -551,6 +556,16 @@
 a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Allarme di sicurezza, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-village-mar-y-sierra.it.html</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>camping-village-mar-y-sierra</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -558,20 +573,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-la-pineta.it.html</t>
+          <t>Camping La Pineta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Camping La Pineta</t>
+          <t>Via della repubblica 3, 62017 Porto Recanati, Italia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>Via della repubblica 3, 62017 Porto Recanati, Italia</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>Situato nella località marchigiana di Porto Recanati, a 25 km da Ancona e a 49 km da Senigallia, il Camping La Pineta vanta un'area giochi per bambini, una spiaggia privata e servizi gratuiti quali la connessione WiFi e un parcheggio privato in loco.
 Alcune sistemazioni dispongono di aria condizionata, di zona pranzo e/o di patio, e su richiesta potrete usufruire di una TV. Avrete a disposizione anche un angolo cottura con frigorifero e fornelli e un bagno privato con vasca o doccia e bidè.
@@ -579,12 +589,12 @@
 Presso la struttura potrete giocare a ping pong e noleggiare biciclette. Il Camping La Pineta dista 13 km da Civitanova Marche e 33 km dall'Aeroporto di Ancona Falconara, il più vicino alla struttura.</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Situato in posizione peculiare direttamente sul mare il Camping Pineta offre al proprio ospite un soggiorno di relax e divertimento. A sud di Porto Recanati, a solo 800 mt dal centro del paese, facilmente raggiungibile tramite  una passeggiata pedonale. A pochi passi dalla rinomata Riviera del Conero e da zone di interesse culturale come Loreto e Recanati. All'interno si potra' trovare bar, ristorante, pizzeria, minimarket, noleggio bici, navetta per il centro e animazione serale e diurna dal 01/07. Cani di piccola taglia ammessi</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>Situato in posizione peculiare direttamente sul mare il Camping Pineta offre al proprio ospite un soggiorno di relax e divertimento. A sud di Porto Recanati, a solo 800 mt dal centro del paese, facilmente raggiungibile tramite  una passeggiata pedonale. A pochi passi dalla rinomata Riviera del Conero e da zone di interesse culturale come Loreto e Recanati. All'interno si potra' trovare bar, ristorante, pizzeria, minimarket, noleggio bici, navetta per il centro e animazione serale e diurna dal 01/07. Cani di piccola taglia ammessi</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Tour o lezioni sulla cultura locale
 a pagamento, Happy hour
@@ -599,6 +609,16 @@
 a pagamento, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-la-pineta.it.html</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>camping-la-pineta</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -606,22 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/saecula.it.html</t>
+          <t>Saecula Natural Village Experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saecula Natural Village Experience</t>
+          <t>Contrada Ripacorvara, 1, 63086 Force, Italia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Contrada Ripacorvara, 1, 63086 Force, Italia</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Hai diritto a uno sconto Genius su Saecula Natural Village Experience! Per risparmiare su questa struttura, ti basta accedere o iscriverti.
+          <t>Hai diritto a uno sconto Genius su Saecula Natural Village Experience! Per risparmiare su questa struttura ti basta accedere.
 Situato a Force, il Saecula Natural Village Experience offre la connessione WiFi gratuita e suite dotate di cucina, area salotto e TV a schermo piatto.
 La nostra è una struttura Agrituristica composta da: ALLOGGI (Appartamenti - Suite Familiare. I nostri quattro moderni appartamenti consentono un sereno soggiorno nel verde caratteristico del nostro villaggio naturale a ridosso del nostro mozzafiato parco di ciliegi); AGRICAMPEGGIO (all’ombra di un vasto ciliegieto, il nostro campeggio dispone di 16 piazzole di 72 mq l’una, disposte in modo da non far mancare spazio e privacy).
 Ogni appartamento dispone di forno, frigorifero, macchina da caffè, piano cottura e bollitore. Alcune unità abitative presentano una zona pranzo e/o una terrazza.
@@ -629,7 +644,7 @@
 San Benedetto. La struttura dista 46 km da Del Tronto e 25 km da Ascoli Piceno. L'Aeroporto più vicino è quello di Ancona Falconara, a 116 km da Saecula Natural Village Experience.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>L'Agriturismo, (nuovo) attivo dal 2018,  è composto da:
 -ALLOGGI - (Appartamenti)
@@ -644,7 +659,7 @@
 - tende + stuoie + sacco a pelo.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bidet, Servizi igienici aggiuntivi, Vasca o doccia, Prodotti da bagno in omaggio, Asciugacapelli, | VISTA: Vista cortile interno, Vista luogo di interesse, Vista montagna, Vista giardino, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | CUCINA: Prodotti per le pulizie, Lavatrice, | ANIMALI: | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Mostre d'arte temporanee
 Non sul posto, Fitness, Vasca all'aperto, Escursioni in bicicletta, Escursionismo, Ping-pong, Solarium, Palestra, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | ALTRI SERVIZI: Armadietti, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Check-in e check-out privati, Sportello bancomat, Deposito bagagli, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Giochi da tavolo/puzzle, Libri, DVD o musica per bambini, Giochi da tavolo/puzzle, Copriprese di sicurezza per bambini, | SERVIZI DI PULIZIA: Servizio pulizie giornaliero
@@ -652,6 +667,16 @@
 a pagamento, | PROTEZIONE E SICUREZZA: Estintori, Accesso con chiavi, | SERVIZI GENERALI: Ciotole per animali domestici, Ceste per animali domestici, Minimarket sul posto, Area fumatori, Aria condizionata, Camera anallergica, Riscaldamento, Possibilità di pranzo al sacco, Cappella o luogo di culto, Disponibilità di camere insonorizzate, Disponibilità di camere familiari, Parrucchiere/salone di bellezza, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/saecula.it.html</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>saecula</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -659,41 +684,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/fattoria-country-village.it.html</t>
+          <t>La Bolla del Borgo. Le Marche tra le stelle.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fattoria country village</t>
+          <t>Via Olmigrandi 72, 60013 Corinaldo, Italia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>contrada fonte san giovanni 3 montecarotto contrada fonte san giovanni 3, 60036 Montecarotto, Italia</t>
+          <t>Situato a Corinaldo, nelle Marche, il campeggio La Bolla del Borgo. Le Marche tra le stelle. offre un giardino. Dotata di un parcheggio privato gratuito, la struttura si trova a 37 km da Ancona.
+Potrete usufruire di lenzuola e asciugamani.
+Il campeggio serve una colazione all'italiana o senza glutine.
+Il Bolla del Borgo. Le Marche tra le stelle. dista 49 km da Riccione e 48 km da Sirolo. L’Aeroporto di Ancona-Falconara è lo scalo più vicino e sorge a 24 km.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hai diritto a uno sconto Genius su fattoria country village! Per risparmiare su questa struttura ti basta accedere.
-Situato a Montecarotto, nelle Marche, il Fattoria Country Village offre sistemazioni con parcheggio privato gratuito.
-A disposizione un bagno in comune completamente attrezzato con bidet e set di cortesia.
-Al mattino vi attende una colazione a buffet o all'italiana.
-Potrete approfittare di un barbecue e rilassarvi in giardino o nell’area salotto in comune.
-Il Fattoria Country Village dista 45 km da Sirolo e 26 km da Senigallia. A 39 km raggiungerete l’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
+          <t>No camping host description</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No camping host description</t>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Doccia, | SPAZI ALL'APERTO: Arredamento da esterno, Giardino, | SERVIZI GENERALI: Camere non fumatori, | ALTRI SERVIZI: Check-in e check-out privati, Check-in e check-out express, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | LINGUE PARLATE: Inglese, Francese, Italiano, Giapponese, | </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: Parcheggio custodito, | INTERNET: | CUCINA: Cucina in comune, | BAGNO: Carta igienica, Bidet, Vasca o doccia, Servizi igienici in comune, WC, Prodotti da bagno in omaggio, Bagno in comune, Vasca, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Barbecue, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Teli da piscina/spiaggia, Sdraio/lettini, Giochi da piscina, Ombrelloni, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | SERVIZI GENERALI: Ciotole per animali domestici, WiFi a pagamento, Sala comune/zona TV, Servizio navetta (a pagamento), Possibilità di pranzo al sacco, Cappella o luogo di culto, Camere/strutture per ospiti disabili, Cassaforte, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
-a pagamento, Pasti per bambini, Snack bar, | ATTIVITÀ: Tiro con l'arco, Happy hour
-a pagamento, Tour in bicicletta, Tour a piedi
-a pagamento, Giro dei pub
-a pagamento, Attrezzatura da badminton, Vasca all'aperto, Staff di animazione, Escursioni in bicicletta, Ping-pong, Pesca, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Check-in e check-out privati, Reception 24 ore su 24, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | SERVIZI BUSINESS: Fax/fotocopiatrice, | LINGUE PARLATE: Inglese, Spagnolo, | </t>
+          <t>https://www.booking.com/hotel/it/la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona.it.html</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona</t>
         </is>
       </c>
     </row>
@@ -703,58 +727,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona.it.html</t>
+          <t>Camping Led Zeppelin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La Bolla del Borgo. Le Marche tra le stelle.</t>
+          <t>5 Contrada Boccabianca, 63064 Cupra Marittima, Italia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>Via Olmigrandi 72, 60013 Corinaldo, Italia</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Situato a Corinaldo, nelle Marche, il campeggio La Bolla del Borgo. Le Marche tra le stelle. offre un giardino. Dotata di un parcheggio privato gratuito, la struttura si trova a 37 km da Ancona.
-Potrete usufruire di lenzuola e asciugamani.
-Il campeggio serve una colazione all'italiana o senza glutine.
-Il Bolla del Borgo. Le Marche tra le stelle. dista 49 km da Riccione e 48 km da Sirolo. L’</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Doccia, | SPAZI ALL'APERTO: Arredamento da esterno, Giardino, | SERVIZI GENERALI: Camere non fumatori, | ALTRI SERVIZI: Check-in e check-out privati, Check-in e check-out express, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | LINGUE PARLATE: Inglese, Francese, Italiano, Giapponese, | </t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-led-zeppelin.it.html</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Camping Led Zeppelin</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5 Contrada Boccabianca, 63064 Cupra Marittima, Italia</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Situato a Cupra Marittima, il Camping Led Zeppelin offre una vista sul proprio giardino, un ristorante, il servizio in camera, un bar, una piscina all’aperto stagionale e un’area giochi per bambini.
 Gli alloggi dispongono di aria condizionata, terrazza, TV a schermo piatto e bagno privato con doccia e set di cortesia. Alcune sistemazioni includono una cucina con microonde e piano cottura.
@@ -762,12 +743,12 @@
 Il Camping Led Zeppelin dista 10 km da San Benedetto del Tronto e 46 km da Porto Recanati. L’Aeroporto d’Abruzzo, lo scalo più vicino, è ubicato a 73 km.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Prodotti da bagno in omaggio, Doccia, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Arredamento da esterno, Terrazza, Giardino, | CUCINA: Frigorifero, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Serate di cinema, Cabaret, Spiaggia, Lezioni di fitness, Intrattenimento serale, Fronte spiaggia, Mini club, Locale notturno/DJ, Staff di animazione, Spiaggia privata
 a pagamento, Karaoke, Area giochi, Pesca, Campo da tennis
@@ -776,27 +757,32 @@
 a pagamento, | ALTRI SERVIZI: Servizio lavanderia, Servizio in camera, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Allarme di sicurezza, Sicurezza 24 ore su 24, | SERVIZI GENERALI: WiFi a pagamento, Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, Ascensore, Disponibilità di camere familiari, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-terrazzo-sul-mare.it.html</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-led-zeppelin.it.html</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>camping-led-zeppelin</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Camping Terrazzo sul mare</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Via Adriatica nord 109, 63064 Cupra Marittima, Italia</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 6 minuti a piedi dalla spiaggia. Situato a Cupra Marittima, a 5 km da Grottammare, il Camping Terrazzo sul mare offre una piscina stagionale all'aperto e il WiFi gratuito.
 Tutte climatizzate, le sistemazioni includono una TV, una cucina interamente attrezzata con zona pranzo e un bagno privato con doccia.
@@ -804,38 +790,43 @@
 Il Camping Terrazzo sul mare dista 10 km da San Benedetto del Tronto e 47 km da Porto Recanati. L’Aeroporto più vicino è quello di Ancona-Falconara, a 85 km.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | VISTA: Vista giardino, Vista mare, | SPAZI ALL'APERTO: Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, | CUCINA: Piano cottura, Utensili da cucina, Cucina, Frigorifero, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ATTIVITÀ: Spiaggia, Spiaggia privata
 a pagamento, Ping-pong, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI DI RISTORAZIONE: Bar, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Sala comune/zona TV, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | SERVIZI GENERALI: Aria condizionata, Ingresso indipendente, Disponibilità di camere familiari, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/europing-village-marsia-neve.it.html</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-terrazzo-sul-mare.it.html</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>camping-terrazzo-sul-mare</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>EUROPING VILLAGE MARSIA Abruzzo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>loc. homo selvatico, 67060 Marsia, Italia</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Situato a Marsia, in Abruzzo, l'EUROPING VILLAGE MARSIA Abruzzo offre un parcheggio privato gratuito.
 Al mattino vi attende una colazione all'italiana.
@@ -843,7 +834,7 @@
 Il campeggio dista 34 km da Tivoli e 30 km da Fiuggi. 57 km dall'Aeroporto di Roma-Ciampino, lo scalo più vicino.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Tutti gli alloggi per la vostra vacanza 
 Marsia vi aspetta con diversi tipi di alloggio, pronti a soddisfare ogni necessità e desiderio. Una struttura dove far star bene e divertire tutta la famiglia, un camping ideale per gli amanti della bici o per chi vuole godersi un weekend all’insegna del relax... Selezionate la categoria di vacanza che fa per voi e prenotate online in tutta sicurezza.
@@ -853,7 +844,7 @@
 Ritrova l'atmosfera di casa tua immergendoti nella natura dei boschi delle splendida Marsia trascorri la tua vacanza nei nuovi Chalet del Camping : nella classica struttura della baita di montagna,</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">SPAZI ALL'APERTO: Area picnic, Barbecue, Giardino, | ANIMALI: | ATTIVITÀ: Happy hour
 a pagamento, Massaggi corpo, Massaggi mani, Massaggi testa, Massaggi piedi, Massaggi collo, Massaggi schiena, Escursionismo, Biliardo
@@ -864,27 +855,32 @@
 a pagamento, | PROTEZIONE E SICUREZZA: Estintori, Allarme di sicurezza, Accesso con chiavi, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Consegna spesa a domicilio, Minimarket sul posto, Area fumatori, Riscaldamento, Possibilità di pranzo al sacco, Disponibilità di camere familiari, Camere non fumatori, Servizio in camera, | LINGUE PARLATE: Inglese, Italiano, Polacco, | </t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/parco-gessilandia.it.html</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/europing-village-marsia-neve.it.html</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>europing-village-marsia-neve</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Parco Gessilandia</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Via Gesso 40 Localita Gesso 40, 61013 Sassofeltrio, Italia</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Situato a Sassofeltrio, il Parco Gessilandia offre una piscina all’aperto stagionale, un bar e un giardino.
 Gli alloggi comprendono un angolo cottura completamente accessoriato con frigorifero e fornelli. Alcune sistemazioni sono provviste di aria condizionata, TV e zona salotto e/o pranzo.
@@ -892,37 +888,42 @@
 Il Parco Gessilandia dista 18 km da Rimini e 16 km da Riccione. L’Aeroporto Internazionale Federico Fellini, il più vicino, si trova a 16 km dalla struttura.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Bidet, Vasca o doccia, WC, Prodotti da bagno in omaggio, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Barbecue, Giardino, | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | SERVIZI DI RISTORAZIONE: Bar, | INTERNET: | PARCHEGGIO: Parcheggio in strada, | SERVIZI GENERALI: Aria condizionata, Disponibilità di camere familiari, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Giochi da piscina, Ombrelloni, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, | LINGUE PARLATE: Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/resort-orizzonti-glamping.it.html</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/parco-gessilandia.it.html</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>parco-gessilandia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Resort Orizzonti Glamping</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>1081 Via Monte Taccone, 63811 Sant'Elpidio a Mare, Italia</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Set in SantʼElpidio a Mare, Resort Orizzonti Glamping offers accommodation with air conditioning and access to a garden with an outdoor swimming pool.
 There is a fully equipped private bathroom with shower and a hairdryer.
@@ -930,37 +931,42 @@
 San Benedetto del Tronto is 36 km from Resort Orizzonti Glamping, while Sirolo is 31 km away. The nearest airport is Ancona Falconara Airport, 48 km from the accommodation.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>La collocazione sopraelevata garantisce un'incantevole vista sulle colline marchigiane e sugli spazi verdi della Riserva naturale, all'orizzonte  scorgono  i monti Sibillini,  dal  Vettore,alla Sibilla  .Questa vista garantisce riservatezza e tranquillità.Attorno un ampio giardino verde con incantevoli ulivi anche secolari, piscina con vista   e con i suoi 3 appartamenti con ingresso indipendenti 2 tende Glampin di lusso completi di ogni confort, .Rende così  il resort Orizzonti un posto unico e speciale.  Siamo noi tutto lo staff di Resort Orizzonti, a prenderci cura di ogni nostro ospite, che aver così accesso non soltanto a una location di pregio ma a un'esperienza esclusiva .</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>La collocazione sopraelevata garantisce un'incantevole vista sulle colline marchigiane e sugli spazi verdi della Riserva naturale, all'orizzonte  scorgono </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | CUCINA: Cucina in comune, Tavolo da pranzo, Utensili da cucina, Frigorifero, | SERVIZI IN CAMERA: Stand appendiabiti, | ANIMALI: | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Possibilità di pranzo al sacco, Servizio lavanderia, | SERVIZI GENERALI: Area fumatori, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/agricampeggio-abbruzzetti.it.html</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/resort-orizzonti-glamping.it.html</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>resort-orizzonti-glamping</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Agricampeggio Abbruzzetti</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Via San Pietro Vecchio, 63900 Marina Palmense, Italia</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Situato a Marina Palmense, l'Agricampeggio Abbruzzetti offre una piscina, un ristorante, un giardino, una vista sulla piscina e la connessione WiFi gratuita.
 Le sistemazioni presentano un patio affacciato sul giardino, una cucina con forno a microonde e frigorifero, e un bagno privato con bidet. Al loro interno troverete un’area salotto e una zona pranzo.
@@ -968,45 +974,50 @@
 L'Agricampeggio Abbruzzetti dista 1,7 km dalla spiaggia di Porto San Giorgio e 70 km dall’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | VISTA: Vista luogo di interesse, Vista montagna, Vista piscina, Vista giardino, Vista mare, | SPAZI ALL'APERTO: Area picnic, Zona pranzo all'aperto, Barbecue, Barbecue, Patio, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Forno a microonde, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | SERVIZI DI RISTORAZIONE: Pasti per bambini
 a pagamento, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio custodito, | ALTRI SERVIZI: Possibilità di pranzo al sacco, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Estintori, | SERVIZI GENERALI: Struttura interamente non fumatori, Zanzariera, Pavimento in marmo o in piastrelle, Ingresso indipendente, Riscaldamento, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Recinto attorno alla piscina, Sdraio/lettini, Ombrelloni, Piscina a sfioro, Piscina con vista, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/antica-dimora-campeggio-fiordaliso.it.html</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/agricampeggio-abbruzzetti.it.html</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>agricampeggio-abbruzzetti</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Antica Dimora - GLAMPING FIORDALISO</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>C.DA CALLARELLA, 62028 Sarnano, Italia</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Situata a Sarnano, nelle Marche, l'ANTICA DIMORA - CAMPEGGIO FIORDALISO offre gratuitamente il WiFi e un parcheggio privato.
 Potrete nuotare nella piscina all'aperto, sciare o andare in bicicletta, o rilassarvi nel giardino e utilizzare il barbecue.
 Il campeggio dista 48 km da Grottammare e 44 km da Porto San Giorgio. L'ANTICA DIMORA - CAMPEGGIO FIORDALISO dista 63 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Il campeggio Fiordaliso è stato pensato per offrire agli ospiti un ambiente naturale e verde, con una bella vista sui Monti Sibillini  godendo di tutti i nuovissimi servizi appena allestiti e di una bella piscina. E' un campeggio per tende e roulotte.
 Abbiamo voluto creare un ambiente per "volare al di fuori del tempo", nei luoghi magici e fantastici di " Alice nel Paese delle Meraviglie".
@@ -1014,7 +1025,7 @@
 C'è un posto che non ha eguali sulla terra....Questo luogo è un luogo unico al mondo, una terra colma di meraviglie, mistero e pericolo. Si dice che per sopravvivere qui bisogna essere matti come un cappellaio. E per fortuna...io lo sono. "</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">PARCHEGGIO: | INTERNET: | BAGNO: Bagno in comune, | SPAZI ALL'APERTO: Area picnic, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Sdraio/lettini, Piscina con vista, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Disponibilità di camere familiari, Camere non fumatori, | ATTIVITÀ: Tour in bicicletta
 a pagamento, Tour a piedi, Escursioni in bicicletta
@@ -1022,27 +1033,32 @@
 Non sul posto, Noleggio biciclette (a pagamento), Sci, | ALTRI SERVIZI: Check-in e check-out express, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Accesso con chiavi, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/villaggio-camping-blu.it.html</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/antica-dimora-campeggio-fiordaliso.it.html</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>antica-dimora-campeggio-fiordaliso</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Camping Blu Fantasy</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Lungomare Italia 3B, 60019 Senigallia, Italia</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Situato sul lungomare, a 4 km da Senigallia, il Camping Blu Fantasy offre appartamenti a ristorazione indipendente, una piscina all’aperto e un giardino con barbecue. Il WiFi è fruibile gratuitamente nelle aree comuni.
 Tutti gli appartamenti sono dotati di aria condizionata, TV a schermo piatto e angolo cottura con forno e frigorifero. Presentano anche un bagno privato con doccia e bidè.
@@ -1050,7 +1066,7 @@
 Il Camping Villaggio Blu si trova a 15 minuti d’auto da Falconara Marittima e a 30 km da Jesi.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>La data di apertura del Villaggio è prevista dal 1° giugno all'11 settembre 2022 compreso, con tutti i servizi operativi, nel rispetto delle norme governative sulla sicurezza e la salute dei nostri ospiti. 
 La biancheria NON è inclusa nel prezzo del soggiorno. Il kit di biancheria completo da letto e da bagno è valido per l'intero soggiorno ed è da noleggiare su richiesta al momento della prenotazione del soggiorno. Il costo per un kit matrimoniale è di 18 Euro, mentre quello del kit singolo di 11,5 Euro. In alternativa si dovrà utilizzare la propria biancheria dal letto e da bagno.
@@ -1058,7 +1074,7 @@
 Vi aspettiamo!</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Barbecue, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Aerobica, Cabaret, Intrattenimento serale, Mini club, Staff di animazione, Vasca idromassaggio/jacuzzi, Freccette, Karaoke, Ping-pong, Area giochi, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali satellitari, | SERVIZI DI RISTORAZIONE: Frutta
 a pagamento, Vino/champagne
@@ -1066,27 +1082,32 @@
 a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Cancelletti di sicurezza per bambini, Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | 2 PISCINE: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Zona acqua bassa, Anche per bambini, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-podere-sei-poorte.it.html</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/villaggio-camping-blu.it.html</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>villaggio-camping-blu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Lodge Holidays - Camping Podere Sei Poorte</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Via Petricci, 61020 Genga, Italia</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Lodge Holidays - Camping. Situato a Genga, il Podere Sei Poorte offre un ristorante, una piscina all'aperto e un bar. 38 km da Cattolica.
 L'alloggio presenta un'area salotto e un angolo cottura con frigorifero e fornelli.
@@ -1094,7 +1115,7 @@
 Il Camping Podere Sei Poorte dista 45 km da Riccione e 23 km da Pesaro. La struttura dista 30 km dall'Aeroporto Internazionale Federico Fellini, lo scalo più vicino.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>If enjoying your holiday might mean more to you than just laying in the sun and could be a combination of just relaxing, cultural development, natural challenges and Italian gastronimical hospitality…………… than Campsite Podere Sei Poorte is your ideal destination. 
 This is truly a fabulous place to spend a holiday and enjoy all the beautiful things life has to offer. The restaurant conjures up delicious pure Italian dishes, à la carte, as well as themed evenings with a pizza buffet, fresh fish, or pasta e basta. 
@@ -1104,32 +1125,37 @@
 Laze in the perfectly appointed Fatboy hammock with panoramic views from your luxury Lodge Holidays lodge.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">PARCHEGGIO: Stazione di ricarica per veicoli elettrici, Parcheggio custodito, | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ACCESSIBILITÀ: Intera unità situata al piano terra, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Aperta tutto l'anno, Sdraio/lettini, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Ingresso indipendente, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Vasca comune (daiyokujo), Intrattenimento serale, Mini club, Escursioni in bicicletta, Noleggio biciclette (a pagamento), Ping-pong, Area giochi, | ALTRI SERVIZI: Sala comune/zona TV, Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/tobacco-road.it.html</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-podere-sei-poorte.it.html</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>camping-podere-sei-poorte</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Tobacco Road camping Sirolo</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Via Peschiera 9, 60020 Sirolo, Italia</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 18 minuti a piedi dalla spiaggia. Situato a Sirolo, il Tobacco Road camping Sirolo offre una vista sulla sua piscina, un bar, un salotto in comune e sistemazioni con WiFi gratuito.
 Le unità dispongono di patio, cucina con frigorifero, zona pranzo, area soggiorno con TV a schermo piatto e bagno privato con doccia.
@@ -1137,12 +1163,12 @@
 I famosi luoghi di interesse nelle vicinanze del Tobacco Road camping Sirolo includono le spiagge di Urbani, San Michele e Numana. L’Aeroporto di Ancona-Falconara, il più vicino, sorge a 23 km.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | VISTA: Vista piscina, | SPAZI ALL'APERTO: Area picnic, Zona pranzo all'aperto, Barbecue, Patio, | CUCINA: Tavolo da pranzo, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo
 Non sul posto, Happy hour
@@ -1154,39 +1180,44 @@
 a pagamento, | ALTRI SERVIZI: Sala comune/zona TV, Check-in e check-out privati, Possibilità di pranzo al sacco, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Insonorizzazione, Ingresso indipendente, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Recinto attorno alla piscina, Sdraio/lettini, Bar a bordo piscina, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/safaritent-glamping-mar-y-sierrra.it.html</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/tobacco-road.it.html</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>tobacco-road</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Safaritent Glamping Mar Y Sierrra</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>via S. Gervasio, 61039 Casa Castellani, Italia</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Situato a Casa Castellani, il Safaritent Glamping Mar Y Sierrra offre un ristorante, una piscina stagionale all'aperto e un bar. La struttura dista 37 km da Urbino e dispone di un parcheggio privato gratuito.
 In loco troverete anche un'area giochi per bambini. Durante il vostro soggiorno al Safaritent Glamping Mar Y Sierrra potrete giocare a ping pong in loco o esplorare i dintorni in bicicletta.
 La struttura dista 41 km da Ancona e 27 km da Pesaro. Il Safaritent Glamping Mar Y Sierrra dista 25 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">PARCHEGGIO: Parcheggio per disabili, | INTERNET: | CUCINA: Utensili da cucina, | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | SPAZI ALL'APERTO: Arredamento da esterni, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Bar a bordo piscina, Ombrelloni, Scivolo d'acqua, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Zanzariera, Parquet o pavimento in legno, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Vino/champagne
 a pagamento, Pasti per bambini, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Snorkeling
@@ -1196,27 +1227,32 @@
 Non sul posto, Ping-pong, Area giochi, Campo da tennis, | ALTRI SERVIZI: Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-norina.it.html</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/safaritent-glamping-mar-y-sierrra.it.html</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>safaritent-glamping-mar-y-sierrra</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Camping Norina</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Via Marina Ardizia 181, 61122 Pesaro, Italia</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Ubicato a Pesaro, il Camping Norina vanta un ristorante, un centro fitness e una spiaggia privata, e offre la connessione WiFi gratuita in tutte le aree.
 Tutti gli alloggi sono climatizzati e dotati di TV a schermo piatto e di bagno privato con asciugacapelli.
@@ -1224,37 +1260,42 @@
 La struttura dista 10 minuti di auto da Pesaro e da Fano e 23 km da Cattolica.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Attrezzature per sport acquatici sul posto, Spiaggia privata, Area giochi, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-paradiso.it.html</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-norina.it.html</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>camping-norina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Camping Paradiso</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Via Rive Del Faro 2, 61121 Pesaro, Italia</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 12 minuti a piedi dalla spiaggia. Ubicato nel parco regionale di San Bartolo, a 850 metri da Castel di Mezzo, il Camping Paradiso offre una piscina all'aperto e un barbecue.
 I bungalow e gli chalet dispongono di una terrazza con vista sulle montagne, di un'area salotto e, in alcuni casi, di un'angolo cottura e di una TV a schermo piatto.
@@ -1262,39 +1303,44 @@
 Il Camping Paradiso si trova a 12 km da Pesaro, e in auto dista 15 minuti dalla stazione di Cattolica e 25 minuti da Riccione.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>La nostra peculiarità è l'atmosfera familiare unita a servizi di qualità. Da sempre i nostri ospiti possono contare sul nostro aiuto per risolvere ogni problematica ed esigenza. Non è raro trovarsi la sera insieme al bar o ristorante a scambiarci battute come amici di vecchia data. Spesso i rapporti continuano anche dopo le vacanze e le famiglie tornano a trovarci per più anni.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Patio, Terrazza, Giardino, | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Cucina, Frigorifero, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, | ATTIVITÀ: Vasca all'aperto, Escursioni in bicicletta, Escursionismo, Freccette, Ping-pong, Area giochi, Pesca
 a pagamento, Campo da golf (nel raggio di 3 km)
 a pagamento, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Sala comune/zona TV, Deposito bagagli, Fax/fotocopiatrice, Possibilità di pranzo al sacco, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Giochi da tavolo/puzzle, | PROTEZIONE E SICUREZZA: Telecamere a circuito chiuso nelle zone in comune, Cassaforte, | SERVIZI GENERALI: Minimarket sul posto, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Piscina con vista, Piscina di acqua salata, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-pineta-urbino.it.html</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-paradiso.it.html</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>camping-paradiso</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Camping Pineta</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Via ca' mignone 5, 61029 Urbino, Italia</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Situato a Urbino, il Camping Pineta offre piscina, ristorante, bar, vista città e WiFi gratuito.
 Le sistemazioni comprendono patio, cucina con frigorifero, zona pranzo, salotto con TV e bagno privato con bidè e asciugacapelli. Per maggiore comodità, potrete usufruire di asciugamani e lenzuola ad un costo aggiuntivo.
@@ -1302,37 +1348,42 @@
 Il Camping Pineta dista 5 km dal Duomo. L’Aeroporto Internazionale Federico Fellini è lo scalo più vicino, a 57 km dalla struttura.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>ll Camping “Pineta” di Urbino è sorto in un'area di circa 22.000 metri quadri a est della citta, situato in una posizione eccellente sia dal punto di vista paesaggistico che da quello funzionale. Infatti si tratta di un terreno in declivio verso la città dal quale si gode un'ottima vista del Centro Storico. ll terreno dove sorge il Camping e in gran parte coperto da una folta pineta dando al campeggiatore uno stretto rapporto con Ia natura e il paesaggio circostante.  I servizi interni del Camping comprendono: bagni, lavandini, Iavelli, lavatoi, docce calde e fredde, fontane e torrette a norme CEE per prese di corrente (220 WT) dislocate in vari punti del terreno, tutto nelle proporzioni previste dalla legge; inoltre funzionano un Bar, un ristorante , piscina e sono disponibili anche bungalow .</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Asciugacapelli, Doccia, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Letto pieghevole, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Patio, Terrazza, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: | SERVIZI GENERALI: Soluzioni anallergiche, Aria condizionata, Zanzariera, Parquet o pavimento in legno, Riscaldamento, Insonorizzazione, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Bar, | ATTIVITÀ: Solarium, | VISTA: Vista luogo di interesse, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-village-costa-verde.it.html</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-pineta-urbino.it.html</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>camping-pineta-urbino</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Camping Village Costa Verde</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Contrada Asola, 62018 Porto Potenza Picena, Italia</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 3 minuti a piedi dalla spiaggia. Situato a Porto Potenza Picena, a 200 metri dalle spiagge di sabbia, il Camping Village Costa Verde offre una piscina all'aperto, un ristorante e la connessione Wi-Fi gratuita nelle aree comuni.
 La struttura metterà a vostra disposizione una reception aperta 24 ore su 24, programmi di intrattenimento serali e per bambini, un'area TV in comune e alcuni servizi a pagamento, come il noleggio di biciclette o di sedie a sdraio per la spiaggia privata.
@@ -1341,12 +1392,12 @@
 Dotato di parcheggio gratuito, il campeggio dista 11,5 km da Porto Sant'Elpidio e 20 minuti di auto dal punto di inizio del Parco Regionale del Conero.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Il Camping Village Costa Verde si trova nelle Marche, a pochi chilometri da una delle aree più suggestive della splendida riviera Adriatica, il Parco naturale del Conero.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Intrattenimento serale, Attrezzature per sport acquatici sul posto
 a pagamento, Staff di animazione, Spiaggia privata
@@ -1358,27 +1409,32 @@
 a pagamento, Riscaldamento, Disponibilità di camere familiari, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-liana.it.html</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-village-costa-verde.it.html</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>camping-village-costa-verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Camping Liana</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Lungomare Leonardo da Vinci 54 ter, 60019 Senigallia, Italia</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Situato a Senigallia, a 26 km da Ancona, il Camping Liana offre un ristorante e la connessione WiFi gratuita.
 La sistemazione dispone di aria condizionata, TV a schermo piatto, cucina interamente attrezzata con zona pranzo e bagno privato completo di doccia. Potrete usufruire di lenzuola e asciugamani a costo aggiuntivo.
@@ -1386,15 +1442,74 @@
 Il Camping Liana dista 35 km da Sirolo e 44 km da Porto Recanati. L’Aeroporto di Ancona-Falconara, lo scalo più vicino, sorge a 27 km.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista luogo di interesse, Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Spiaggia privata
 a pagamento, | AREA SOGGIORNO: Zona pranzo, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Zanzariera, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-liana.it.html</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>camping-liana</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fattoria country village</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>contrada fonte san giovanni 3 montecarotto contrada fonte san giovanni 3, 60036 Montecarotto, Italia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Hai diritto a uno sconto Genius su fattoria country village! Per risparmiare su questa struttura ti basta accedere.
+Situato a Montecarotto, nelle Marche, il Fattoria Country Village offre sistemazioni con parcheggio privato gratuito.
+A disposizione un bagno in comune completamente attrezzato con bidet e set di cortesia.
+Al mattino vi attende una colazione a buffet o all'italiana.
+Potrete approfittare di un barbecue e rilassarvi in giardino o nell’area salotto in comune.
+Il Fattoria Country Village dista 45 km da Sirolo e 26 km da Senigallia. A 39 km raggiungerete l’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: Parcheggio custodito, | INTERNET: | CUCINA: Cucina in comune, | BAGNO: Carta igienica, Bidet, Vasca o doccia, Servizi igienici in comune, WC, Prodotti da bagno in omaggio, Bagno in comune, Vasca, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Barbecue, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Teli da piscina/spiaggia, Sdraio/lettini, Giochi da piscina, Ombrelloni, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | SERVIZI GENERALI: Ciotole per animali domestici, WiFi a pagamento, Sala comune/zona TV, Servizio navetta (a pagamento), Possibilità di pranzo al sacco, Cappella o luogo di culto, Camere/strutture per ospiti disabili, Cassaforte, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
+a pagamento, Pasti per bambini, Snack bar, | ATTIVITÀ: Tiro con l'arco, Happy hour
+a pagamento, Tour in bicicletta, Tour a piedi
+a pagamento, Giro dei pub
+a pagamento, Attrezzatura da badminton, Vasca all'aperto, Staff di animazione, Escursioni in bicicletta, Ping-pong, Pesca, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Check-in e check-out privati, Reception 24 ore su 24, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | SERVIZI BUSINESS: Fax/fotocopiatrice, | LINGUE PARLATE: Inglese, Spagnolo, | </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/fattoria-country-village.it.html</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>fattoria-country-village</t>
         </is>
       </c>
     </row>
@@ -1404,20 +1519,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/bungalow-verde-mare.it.html</t>
+          <t>Bungalow Verde Mare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bungalow Verde Mare</t>
+          <t>Lungomare Marina Palmense, 63900 Marina Palmense, Italia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
-        <is>
-          <t>Lungomare Marina Palmense, 63900 Marina Palmense, Italia</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
         <is>
           <t>Offering sea views and a seasonal outdoor swimming pool, Bungalow Verde Mare offers accommodation conveniently located in Marina Palmense, within a short distance of Porto San Giorgio Beach.
 The camping offers a seating area with a flat-screen TV and a private bathroom with a hairdryer and bidet.
@@ -1425,12 +1535,12 @@
 The nearest airport is Ancona Falconara Airport, 62 km from the accommodation.</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Bidet, Bagno privato, WC, Asciugacapelli, | VISTA: Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Lavatrice, Frigorifero, | SERVIZI IN CAMERA: Divano letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Happy hour
 a pagamento, Spiaggia, Attrezzatura da tennis
@@ -1441,6 +1551,16 @@
 a pagamento, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/bungalow-verde-mare.it.html</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>bungalow-verde-mare</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1448,20 +1568,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-spiaggia-di-velluto.it.html</t>
+          <t>Camping Spiaggia di Velluto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Camping Spiaggia di Velluto</t>
+          <t>Lungomare Leonardo da Vinci, 60019 Senigallia, Italia</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
-        <is>
-          <t>Lungomare Leonardo da Vinci, 60019 Senigallia, Italia</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Situato a Senigallia, nelle Marche, il Camping Spiaggia di Velluto offre sistemazioni con parcheggio privato gratuito.
 Tutti gli alloggi comprendono divano, salotto, TV via cavo a schermo piatto, angolo cottura ben attrezzato e bagno privato con bidè e doccia. Per maggiore comodità, potrete usufruire di asciugamani e lenzuola a un costo aggiuntivo.
@@ -1470,7 +1585,7 @@
 La struttura si trova a 34 km da Sirolo e a 43 km da Porto Recanati. L'Aeroporto di Ancona-Falconara è lo scalo più vicino, a 12 km dal Camping Spiaggia di Velluto.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Dal diradare delle splendide colline marchigiane al mare si trova il camping Spiaggia di Velluto di Senigallia, polo turistico delle Marche, che accoglie da sempre visitatori da ogni parte del mondo.
 Il nostro campeggio, con una superficie di 15.000 mq., si affacciata direttamente sulle spiagge basse e sabbiose del litorale adriatico ed è il luogo ideale per famiglie e bambini in cui trascorrere le vostre vacanze in relax.
@@ -1478,10 +1593,20 @@
 Il servizio di pensione completa o mezza pensione è disponibile presso un ristorante convenzionato situato vicino alla nostra struttura.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Terrazza, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, | ATTIVITÀ: Spiaggia, Fronte spiaggia, Spiaggia privata, Windsurf, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, Scrivania, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali via cavo, TV, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio navetta, Servizio navetta (gratuito), Servizio lavanderia
 a pagamento, | PROTEZIONE E SICUREZZA: Estintori, | SERVIZI GENERALI: Aria condizionata, Zanzariera, Ingresso indipendente, Riscaldamento, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | SERVIZI BENESSERE: Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-spiaggia-di-velluto.it.html</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>camping-spiaggia-di-velluto</t>
         </is>
       </c>
     </row>
@@ -1491,20 +1616,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/glamping-marche-nascoste-tenda-e-intero-alloggio.it.html</t>
+          <t>Glamping Marche Nascoste Tenda e intero alloggio</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Glamping Marche Nascoste Tenda e intero alloggio</t>
+          <t>41 Strada Provinciale 54, 62020 Penna San Giovanni, Italia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
-        <is>
-          <t>41 Strada Provinciale 54, 62020 Penna San Giovanni, Italia</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>Located in Penna San Giovanni in the Marche region, Glamping Marche Nascoste Tenda e intero alloggio features a garden. The property is 39 km from Grottammare and free private parking is provided.
 The tented camp also provides a fully equipped kitchen with a fridge, a seating area, a washing machine and 1 bathroom with a bidet and a bath.
@@ -1512,17 +1632,27 @@
 San Benedetto del Tronto is 41 km from Glamping Marche Nascoste Tenda, while Porto Recanati is 47 km away. The nearest airport is Ancona Falconara Airport, 61 km from the accommodation.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Nel piccolo borgo di Penna San Giovanni potrete soggiornare nella tenda Sibilla ,all'ombra degli alberi del nostro giardino con vista sui Sibillini, tra ulivi e fiori. Tenda di 5 m di diametro arredata (max 4 pers.) e intero alloggio privato con bagno, cucina, una camera (altre 2 pers.), sala e intrattenimento per vivere momenti meravigliosi. L'alloggio può ospitare fino a 6 persone dello stesso nucleo.
 Colazione con prodotti freschi locali. Noleggio bici, trekking, spiagge nelle vicinanze e molto altro!
 La nostra filosofia: green, fai da te, riutilizzo per limitare l'impatto ambientale.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Tostapane, Piano cottura, Forno, Utensili da cucina, Cucina, Lavatrice, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Asciugamani, Bidet, Vasca o doccia, Servizi igienici in comune, Bagno privato, WC, Prodotti da bagno in omaggio, Asciugacapelli, Vasca, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | SERVIZI GENERALI: Zanzariera, Pavimento in marmo o in piastrelle, Ingresso indipendente, Riscaldamento, Ventilatore, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Frutta, Vino/champagne
 a pagamento, Possibilità di colazione in camera, Bollitore tè/macchina caffè, | ATTIVITÀ: Freccette, Ping-pong, | ALTRI SERVIZI: Ciotole per animali domestici, Servizio lavanderia, | VISTA: Vista montagna, Vista giardino, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, Giochi da tavolo/puzzle, | LINGUE PARLATE: Tedesco, Inglese, Spagnolo, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/glamping-marche-nascoste-tenda-e-intero-alloggio.it.html</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>glamping-marche-nascoste-tenda-e-intero-alloggio</t>
         </is>
       </c>
     </row>

--- a/datasets/general_data_dataset_booking.xlsx
+++ b/datasets/general_data_dataset_booking.xlsx
@@ -526,62 +526,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camping Village Mar y Sierra</t>
+          <t>Camping La Pineta</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Strada San Gervasio 3, 61039 San Costanzo, Italia</t>
+          <t>Via della repubblica 3, 62017 Porto Recanati, Italia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>Situato a San Costanzo, il Camping Village Mar y Sierra vanta una piscina all'aperto, la connessione WiFi gratuita nelle aree comuni e camere climatizzate, in alcuni casi con terrazza.
-Ciascuna sistemazione presenta anche una TV a schermo piatto, una scrivania e un bagno privato con set di cortesia.
-Il campeggio comprende anche un campo da tennis, servizi per riunioni, un salone comune e uno staff dedicato per l'intrattenimento.
-Completo di parcheggio gratuito, il Camping Village Mar y Sierra dista, in auto, 10 minuti dalle spiagge della zona e 40 minuti da Pesaro.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Terrazza solarium, Barbecue, Terrazza, Giardino, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Spiaggia, Armadietti per fitness/spa, Attrezzatura da tennis, Parco acquatico
-Non sul posto
-a pagamento, Intrattenimento serale, Ping-pong, Area giochi, Sala giochi, Campo da tennis, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
-a pagamento, Pasti per bambini, Menù per diete particolari (su richiesta), Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | ALTRI SERVIZI: Sala comune/zona TV, Servizio concierge, Deposito bagagli, Banco escursioni, Spazi per riunioni/banchetti
-a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Allarme di sicurezza, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-village-mar-y-sierra.it.html</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>camping-village-mar-y-sierra</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Camping La Pineta</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Via della repubblica 3, 62017 Porto Recanati, Italia</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
         <is>
           <t>Situato nella località marchigiana di Porto Recanati, a 25 km da Ancona e a 49 km da Senigallia, il Camping La Pineta vanta un'area giochi per bambini, una spiaggia privata e servizi gratuiti quali la connessione WiFi e un parcheggio privato in loco.
 Alcune sistemazioni dispongono di aria condizionata, di zona pranzo e/o di patio, e su richiesta potrete usufruire di una TV. Avrete a disposizione anche un angolo cottura con frigorifero e fornelli e un bagno privato con vasca o doccia e bidè.
@@ -589,12 +542,12 @@
 Presso la struttura potrete giocare a ping pong e noleggiare biciclette. Il Camping La Pineta dista 13 km da Civitanova Marche e 33 km dall'Aeroporto di Ancona Falconara, il più vicino alla struttura.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Situato in posizione peculiare direttamente sul mare il Camping Pineta offre al proprio ospite un soggiorno di relax e divertimento. A sud di Porto Recanati, a solo 800 mt dal centro del paese, facilmente raggiungibile tramite  una passeggiata pedonale. A pochi passi dalla rinomata Riviera del Conero e da zone di interesse culturale come Loreto e Recanati. All'interno si potra' trovare bar, ristorante, pizzeria, minimarket, noleggio bici, navetta per il centro e animazione serale e diurna dal 01/07. Cani di piccola taglia ammessi</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Tour o lezioni sulla cultura locale
 a pagamento, Happy hour
@@ -609,32 +562,32 @@
 a pagamento, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.booking.com/hotel/it/camping-la-pineta.it.html</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>camping-la-pineta</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Saecula Natural Village Experience</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Contrada Ripacorvara, 1, 63086 Force, Italia</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hai diritto a uno sconto Genius su Saecula Natural Village Experience! Per risparmiare su questa struttura ti basta accedere.
 Situato a Force, il Saecula Natural Village Experience offre la connessione WiFi gratuita e suite dotate di cucina, area salotto e TV a schermo piatto.
@@ -644,7 +597,7 @@
 San Benedetto. La struttura dista 46 km da Del Tronto e 25 km da Ascoli Piceno. L'Aeroporto più vicino è quello di Ancona Falconara, a 116 km da Saecula Natural Village Experience.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>L'Agriturismo, (nuovo) attivo dal 2018,  è composto da:
 -ALLOGGI - (Appartamenti)
@@ -659,7 +612,7 @@
 - tende + stuoie + sacco a pelo.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bidet, Servizi igienici aggiuntivi, Vasca o doccia, Prodotti da bagno in omaggio, Asciugacapelli, | VISTA: Vista cortile interno, Vista luogo di interesse, Vista montagna, Vista giardino, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | CUCINA: Prodotti per le pulizie, Lavatrice, | ANIMALI: | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Mostre d'arte temporanee
 Non sul posto, Fitness, Vasca all'aperto, Escursioni in bicicletta, Escursionismo, Ping-pong, Solarium, Palestra, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | ALTRI SERVIZI: Armadietti, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Check-in e check-out privati, Sportello bancomat, Deposito bagagli, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Giochi da tavolo/puzzle, Libri, DVD o musica per bambini, Giochi da tavolo/puzzle, Copriprese di sicurezza per bambini, | SERVIZI DI PULIZIA: Servizio pulizie giornaliero
@@ -667,14 +620,63 @@
 a pagamento, | PROTEZIONE E SICUREZZA: Estintori, Accesso con chiavi, | SERVIZI GENERALI: Ciotole per animali domestici, Ceste per animali domestici, Minimarket sul posto, Area fumatori, Aria condizionata, Camera anallergica, Riscaldamento, Possibilità di pranzo al sacco, Cappella o luogo di culto, Disponibilità di camere insonorizzate, Disponibilità di camere familiari, Parrucchiere/salone di bellezza, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/saecula.it.html</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>saecula</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fattoria country village</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>contrada fonte san giovanni 3 montecarotto contrada fonte san giovanni 3, 60036 Montecarotto, Italia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hai diritto a uno sconto Genius su fattoria country village! Per risparmiare su questa struttura ti basta accedere.
+Situato a Montecarotto, nelle Marche, il Fattoria Country Village offre sistemazioni con parcheggio privato gratuito.
+A disposizione un bagno in comune completamente attrezzato con bidet e set di cortesia.
+Al mattino vi attende una colazione a buffet o all'italiana.
+Potrete approfittare di un barbecue e rilassarvi in giardino o nell’area salotto in comune.
+Il Fattoria Country Village dista 45 km da Sirolo e 26 km da Senigallia. A 39 km raggiungerete l’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: Parcheggio custodito, | INTERNET: | CUCINA: Cucina in comune, | BAGNO: Carta igienica, Bidet, Vasca o doccia, Servizi igienici in comune, WC, Prodotti da bagno in omaggio, Bagno in comune, Vasca, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Barbecue, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Teli da piscina/spiaggia, Sdraio/lettini, Giochi da piscina, Ombrelloni, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | SERVIZI GENERALI: Ciotole per animali domestici, WiFi a pagamento, Sala comune/zona TV, Servizio navetta (a pagamento), Possibilità di pranzo al sacco, Cappella o luogo di culto, Camere/strutture per ospiti disabili, Cassaforte, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
+a pagamento, Pasti per bambini, Snack bar, | ATTIVITÀ: Tiro con l'arco, Happy hour
+a pagamento, Tour in bicicletta, Tour a piedi
+a pagamento, Giro dei pub
+a pagamento, Attrezzatura da badminton, Vasca all'aperto, Staff di animazione, Escursioni in bicicletta, Ping-pong, Pesca, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Check-in e check-out privati, Reception 24 ore su 24, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | SERVIZI BUSINESS: Fax/fotocopiatrice, | LINGUE PARLATE: Inglese, Spagnolo, | </t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/saecula.it.html</t>
+          <t>https://www.booking.com/hotel/it/fattoria-country-village.it.html</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>saecula</t>
+          <t>fattoria-country-village</t>
         </is>
       </c>
     </row>
@@ -684,58 +686,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>La Bolla del Borgo. Le Marche tra le stelle.</t>
+          <t>Camping Led Zeppelin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Via Olmigrandi 72, 60013 Corinaldo, Italia</t>
+          <t>5 Contrada Boccabianca, 63064 Cupra Marittima, Italia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>Situato a Corinaldo, nelle Marche, il campeggio La Bolla del Borgo. Le Marche tra le stelle. offre un giardino. Dotata di un parcheggio privato gratuito, la struttura si trova a 37 km da Ancona.
-Potrete usufruire di lenzuola e asciugamani.
-Il campeggio serve una colazione all'italiana o senza glutine.
-Il Bolla del Borgo. Le Marche tra le stelle. dista 49 km da Riccione e 48 km da Sirolo. L’Aeroporto di Ancona-Falconara è lo scalo più vicino e sorge a 24 km.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Doccia, | SPAZI ALL'APERTO: Arredamento da esterno, Giardino, | SERVIZI GENERALI: Camere non fumatori, | ALTRI SERVIZI: Check-in e check-out privati, Check-in e check-out express, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | LINGUE PARLATE: Inglese, Francese, Italiano, Giapponese, | </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona.it.html</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Camping Led Zeppelin</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5 Contrada Boccabianca, 63064 Cupra Marittima, Italia</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Situato a Cupra Marittima, il Camping Led Zeppelin offre una vista sul proprio giardino, un ristorante, il servizio in camera, un bar, una piscina all’aperto stagionale e un’area giochi per bambini.
 Gli alloggi dispongono di aria condizionata, terrazza, TV a schermo piatto e bagno privato con doccia e set di cortesia. Alcune sistemazioni includono una cucina con microonde e piano cottura.
@@ -743,12 +702,12 @@
 Il Camping Led Zeppelin dista 10 km da San Benedetto del Tronto e 46 km da Porto Recanati. L’Aeroporto d’Abruzzo, lo scalo più vicino, è ubicato a 73 km.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Prodotti da bagno in omaggio, Doccia, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Arredamento da esterno, Terrazza, Giardino, | CUCINA: Frigorifero, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Serate di cinema, Cabaret, Spiaggia, Lezioni di fitness, Intrattenimento serale, Fronte spiaggia, Mini club, Locale notturno/DJ, Staff di animazione, Spiaggia privata
 a pagamento, Karaoke, Area giochi, Pesca, Campo da tennis
@@ -757,14 +716,57 @@
 a pagamento, | ALTRI SERVIZI: Servizio lavanderia, Servizio in camera, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Allarme di sicurezza, Sicurezza 24 ore su 24, | SERVIZI GENERALI: WiFi a pagamento, Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, Ascensore, Disponibilità di camere familiari, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-led-zeppelin.it.html</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>camping-led-zeppelin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>La Bolla del Borgo. Le Marche tra le stelle.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Via Olmigrandi 72, 60013 Corinaldo, Italia</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Situato a Corinaldo, nelle Marche, il campeggio La Bolla del Borgo. Le Marche tra le stelle. offre un giardino. Dotata di un parcheggio privato gratuito, la struttura si trova a 37 km da Ancona.
+Potrete usufruire di lenzuola e asciugamani.
+Il campeggio serve una colazione all'italiana o senza glutine.
+Il Bolla del Borgo. Le Marche tra le stelle. dista 49 km da Riccione e 48 km da Sirolo. L’Aeroporto di Ancona-Falconara è lo scalo più vicino e sorge a 24 km.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Doccia, | SPAZI ALL'APERTO: Arredamento da esterno, Giardino, | SERVIZI GENERALI: Camere non fumatori, | ALTRI SERVIZI: Check-in e check-out privati, Check-in e check-out express, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | LINGUE PARLATE: Inglese, Francese, Italiano, Giapponese, | </t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-led-zeppelin.it.html</t>
+          <t>https://www.booking.com/hotel/it/la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona.it.html</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>camping-led-zeppelin</t>
+          <t>la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona</t>
         </is>
       </c>
     </row>
@@ -915,40 +917,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Resort Orizzonti Glamping</t>
+          <t>Camping Village Mar y Sierra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1081 Via Monte Taccone, 63811 Sant'Elpidio a Mare, Italia</t>
+          <t>Strada San Gervasio 3, 61039 San Costanzo, Italia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Set in SantʼElpidio a Mare, Resort Orizzonti Glamping offers accommodation with air conditioning and access to a garden with an outdoor swimming pool.
-There is a fully equipped private bathroom with shower and a hairdryer.
-The tented camp provides a barbecue.
-San Benedetto del Tronto is 36 km from Resort Orizzonti Glamping, while Sirolo is 31 km away. The nearest airport is Ancona Falconara Airport, 48 km from the accommodation.</t>
+          <t>Situato a San Costanzo, il Camping Village Mar y Sierra vanta una piscina all'aperto, la connessione WiFi gratuita nelle aree comuni e camere climatizzate, in alcuni casi con terrazza.
+Ciascuna sistemazione presenta anche una TV a schermo piatto, una scrivania e un bagno privato con set di cortesia.
+Il campeggio comprende anche un campo da tennis, servizi per riunioni, un salone comune e uno staff dedicato per l'intrattenimento.
+Completo di parcheggio gratuito, il Camping Village Mar y Sierra dista, in auto, 10 minuti dalle spiagge della zona e 40 minuti da Pesaro.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La collocazione sopraelevata garantisce un'incantevole vista sulle colline marchigiane e sugli spazi verdi della Riserva naturale, all'orizzonte  scorgono </t>
+          <t>No camping host description</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | CUCINA: Cucina in comune, Tavolo da pranzo, Utensili da cucina, Frigorifero, | SERVIZI IN CAMERA: Stand appendiabiti, | ANIMALI: | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Possibilità di pranzo al sacco, Servizio lavanderia, | SERVIZI GENERALI: Area fumatori, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Italiano, | </t>
+          <t xml:space="preserve">BAGNO: Carta igienica, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Terrazza solarium, Barbecue, Terrazza, Giardino, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Spiaggia, Armadietti per fitness/spa, Attrezzatura da tennis, Parco acquatico
+Non sul posto
+a pagamento, Intrattenimento serale, Ping-pong, Area giochi, Sala giochi, Campo da tennis, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
+a pagamento, Pasti per bambini, Menù per diete particolari (su richiesta), Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | ALTRI SERVIZI: Sala comune/zona TV, Servizio concierge, Deposito bagagli, Banco escursioni, Spazi per riunioni/banchetti
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Allarme di sicurezza, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/resort-orizzonti-glamping.it.html</t>
+          <t>https://www.booking.com/hotel/it/camping-village-mar-y-sierra.it.html</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>resort-orizzonti-glamping</t>
+          <t>camping-village-mar-y-sierra</t>
         </is>
       </c>
     </row>
@@ -958,156 +964,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Agricampeggio Abbruzzetti</t>
+          <t>Lodge Holidays - Camping Podere Sei Poorte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Via San Pietro Vecchio, 63900 Marina Palmense, Italia</t>
+          <t>Via Petricci, 61020 Genga, Italia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>Situato a Marina Palmense, l'Agricampeggio Abbruzzetti offre una piscina, un ristorante, un giardino, una vista sulla piscina e la connessione WiFi gratuita.
-Le sistemazioni presentano un patio affacciato sul giardino, una cucina con forno a microonde e frigorifero, e un bagno privato con bidet. Al loro interno troverete un’area salotto e una zona pranzo.
-Il campeggio mette a vostra disposizione un barbecue.
-L'Agricampeggio Abbruzzetti dista 1,7 km dalla spiaggia di Porto San Giorgio e 70 km dall’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | VISTA: Vista luogo di interesse, Vista montagna, Vista piscina, Vista giardino, Vista mare, | SPAZI ALL'APERTO: Area picnic, Zona pranzo all'aperto, Barbecue, Barbecue, Patio, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Forno a microonde, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | SERVIZI DI RISTORAZIONE: Pasti per bambini
-a pagamento, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio custodito, | ALTRI SERVIZI: Possibilità di pranzo al sacco, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Estintori, | SERVIZI GENERALI: Struttura interamente non fumatori, Zanzariera, Pavimento in marmo o in piastrelle, Ingresso indipendente, Riscaldamento, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Recinto attorno alla piscina, Sdraio/lettini, Ombrelloni, Piscina a sfioro, Piscina con vista, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/agricampeggio-abbruzzetti.it.html</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>agricampeggio-abbruzzetti</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Antica Dimora - GLAMPING FIORDALISO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>C.DA CALLARELLA, 62028 Sarnano, Italia</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Situata a Sarnano, nelle Marche, l'ANTICA DIMORA - CAMPEGGIO FIORDALISO offre gratuitamente il WiFi e un parcheggio privato.
-Potrete nuotare nella piscina all'aperto, sciare o andare in bicicletta, o rilassarvi nel giardino e utilizzare il barbecue.
-Il campeggio dista 48 km da Grottammare e 44 km da Porto San Giorgio. L'ANTICA DIMORA - CAMPEGGIO FIORDALISO dista 63 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Il campeggio Fiordaliso è stato pensato per offrire agli ospiti un ambiente naturale e verde, con una bella vista sui Monti Sibillini  godendo di tutti i nuovissimi servizi appena allestiti e di una bella piscina. E' un campeggio per tende e roulotte.
-Abbiamo voluto creare un ambiente per "volare al di fuori del tempo", nei luoghi magici e fantastici di " Alice nel Paese delle Meraviglie".
-Potrete alloggiare in delle bellissime roulotte rivisitate dove incontrerete lo Stregatto o il  Bianconiglio o piuttosto il Cappellaio Magico perchè la nostra parola d'ordine è MERAVIGLIARSI SEMPRE....meravigliarsi delle lucciole che ci fanno luce nelle sere di giugno , delle stelle così brillanti che sembra di toccare con la mano, dei concerti al chiaro di luna intonati dalle nostre rane, dalla tenerezza di tutti i nostri amici della fattoria che ci fanno da cornice. 
-C'è un posto che non ha eguali sulla terra....Questo luogo è un luogo unico al mondo, una terra colma di meraviglie, mistero e pericolo. Si dice che per sopravvivere qui bisogna essere matti come un cappellaio. E per fortuna...io lo sono. "</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | BAGNO: Bagno in comune, | SPAZI ALL'APERTO: Area picnic, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Sdraio/lettini, Piscina con vista, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Disponibilità di camere familiari, Camere non fumatori, | ATTIVITÀ: Tour in bicicletta
-a pagamento, Tour a piedi, Escursioni in bicicletta
-Non sul posto, Escursionismo
-Non sul posto, Noleggio biciclette (a pagamento), Sci, | ALTRI SERVIZI: Check-in e check-out express, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Accesso con chiavi, | LINGUE PARLATE: Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/antica-dimora-campeggio-fiordaliso.it.html</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>antica-dimora-campeggio-fiordaliso</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Camping Blu Fantasy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Lungomare Italia 3B, 60019 Senigallia, Italia</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Situato sul lungomare, a 4 km da Senigallia, il Camping Blu Fantasy offre appartamenti a ristorazione indipendente, una piscina all’aperto e un giardino con barbecue. Il WiFi è fruibile gratuitamente nelle aree comuni.
-Tutti gli appartamenti sono dotati di aria condizionata, TV a schermo piatto e angolo cottura con forno e frigorifero. Presentano anche un bagno privato con doccia e bidè.
-I più piccoli apprezzeranno il programma di intrattenimento e l’area giochi a loro dedicati. Tra i servizi troverete inoltre un bar, un minimarket e un ristorante esterno convenzionato con trattamento di mezza pensione e pensione completa.
-Il Camping Villaggio Blu si trova a 15 minuti d’auto da Falconara Marittima e a 30 km da Jesi.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>La data di apertura del Villaggio è prevista dal 1° giugno all'11 settembre 2022 compreso, con tutti i servizi operativi, nel rispetto delle norme governative sulla sicurezza e la salute dei nostri ospiti. 
-La biancheria NON è inclusa nel prezzo del soggiorno. Il kit di biancheria completo da letto e da bagno è valido per l'intero soggiorno ed è da noleggiare su richiesta al momento della prenotazione del soggiorno. Il costo per un kit matrimoniale è di 18 Euro, mentre quello del kit singolo di 11,5 Euro. In alternativa si dovrà utilizzare la propria biancheria dal letto e da bagno.
-Il servizio spiaggia NON è incluso nel prezzo del soggiorno. Vi sono 2 stabilimenti balneari con sabbia aggiunta nelle vicinanze; spiaggia convenzionata "TRILLO 148" a 600 metri oppure spiaggia NON convenzionata "Bahya Blanca"a 150 metri (più piccola e meno attrezzata). Spiaggia libera di ghiaia con fondale sabbioso di fronte a noi, a 50 metri.
-Vi aspettiamo!</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Barbecue, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Aerobica, Cabaret, Intrattenimento serale, Mini club, Staff di animazione, Vasca idromassaggio/jacuzzi, Freccette, Karaoke, Ping-pong, Area giochi, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali satellitari, | SERVIZI DI RISTORAZIONE: Frutta
-a pagamento, Vino/champagne
-a pagamento, Buffet per bambini, Pasti per bambini, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio in strada, | ALTRI SERVIZI: Servizio navetta, Sala comune/zona TV, Servizio navetta (gratuito), Possibilità di pranzo al sacco, Servizio lavanderia
-a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Cancelletti di sicurezza per bambini, Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | 2 PISCINE: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Zona acqua bassa, Anche per bambini, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/villaggio-camping-blu.it.html</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>villaggio-camping-blu</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Lodge Holidays - Camping Podere Sei Poorte</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Via Petricci, 61020 Genga, Italia</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>Lodge Holidays - Camping. Situato a Genga, il Podere Sei Poorte offre un ristorante, una piscina all'aperto e un bar. 38 km da Cattolica.
 L'alloggio presenta un'area salotto e un angolo cottura con frigorifero e fornelli.
@@ -1115,7 +980,7 @@
 Il Camping Podere Sei Poorte dista 45 km da Riccione e 23 km da Pesaro. La struttura dista 30 km dall'Aeroporto Internazionale Federico Fellini, lo scalo più vicino.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>If enjoying your holiday might mean more to you than just laying in the sun and could be a combination of just relaxing, cultural development, natural challenges and Italian gastronimical hospitality…………… than Campsite Podere Sei Poorte is your ideal destination. 
 This is truly a fabulous place to spend a holiday and enjoy all the beautiful things life has to offer. The restaurant conjures up delicious pure Italian dishes, à la carte, as well as themed evenings with a pizza buffet, fresh fish, or pasta e basta. 
@@ -1125,19 +990,157 @@
 Laze in the perfectly appointed Fatboy hammock with panoramic views from your luxury Lodge Holidays lodge.</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: Stazione di ricarica per veicoli elettrici, Parcheggio custodito, | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ACCESSIBILITÀ: Intera unità situata al piano terra, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Aperta tutto l'anno, Sdraio/lettini, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Ingresso indipendente, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Vasca comune (daiyokujo), Intrattenimento serale, Mini club, Escursioni in bicicletta, Noleggio biciclette (a pagamento), Ping-pong, Area giochi, | ALTRI SERVIZI: Sala comune/zona TV, Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-podere-sei-poorte.it.html</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>camping-podere-sei-poorte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Safaritent Glamping Mar Y Sierrra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>via S. Gervasio, 61039 Casa Castellani, Italia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Situato a Casa Castellani, il Safaritent Glamping Mar Y Sierrra offre un ristorante, una piscina stagionale all'aperto e un bar. La struttura dista 37 km da Urbino e dispone di un parcheggio privato gratuito.
+In loco troverete anche un'area giochi per bambini. Durante il vostro soggiorno al Safaritent Glamping Mar Y Sierrra potrete giocare a ping pong in loco o esplorare i dintorni in bicicletta.
+La struttura dista 41 km da Ancona e 27 km da Pesaro. Il Safaritent Glamping Mar Y Sierrra dista 25 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: Parcheggio per disabili, | INTERNET: | CUCINA: Utensili da cucina, | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | SPAZI ALL'APERTO: Arredamento da esterni, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Bar a bordo piscina, Ombrelloni, Scivolo d'acqua, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Zanzariera, Parquet o pavimento in legno, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Vino/champagne
+a pagamento, Pasti per bambini, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Snorkeling
+Non sul posto, Equitazione
+Non sul posto, Escursioni in bicicletta
+Non sul posto, Vasca idromassaggio/jacuzzi, Windsurf
+Non sul posto, Ping-pong, Area giochi, Campo da tennis, | ALTRI SERVIZI: Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/safaritent-glamping-mar-y-sierrra.it.html</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>safaritent-glamping-mar-y-sierrra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Antica Dimora - GLAMPING FIORDALISO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C.DA CALLARELLA, 62028 Sarnano, Italia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Situata a Sarnano, nelle Marche, l'ANTICA DIMORA - CAMPEGGIO FIORDALISO offre gratuitamente il WiFi e un parcheggio privato.
+Potrete nuotare nella piscina all'aperto, sciare o andare in bicicletta, o rilassarvi nel giardino e utilizzare il barbecue.
+Il campeggio dista 48 km da Grottammare e 44 km da Porto San Giorgio. L'ANTICA DIMORA - CAMPEGGIO FIORDALISO dista 63 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Il campeggio Fiordaliso è stato pensato per offrire agli ospiti un ambiente naturale e verde, con una bella vista sui Monti Sibillini  godendo di tutti i nuovissimi servizi appena allestiti e di una bella piscina. E' un campeggio per tende e roulotte.
+Abbiamo voluto creare un ambiente per "volare al di fuori del tempo", nei luoghi magici e fantastici di " Alice nel Paese delle Meraviglie".
+Potrete alloggiare in delle bellissime roulotte rivisitate dove incontrerete lo Stregatto o il  Bianconiglio o piuttosto il Cappellaio Magico perchè la nostra parola d'ordine è MERAVIGLIARSI SEMPRE....meravigliarsi delle lucciole che ci fanno luce nelle sere di giugno , delle stelle così brillanti che sembra di toccare con la mano, dei concerti al chiaro di luna intonati dalle nostre rane, dalla tenerezza di tutti i nostri amici della fattoria che ci fanno da cornice. 
+C'è un posto che non ha eguali sulla terra....Questo luogo è un luogo unico al mondo, una terra colma di meraviglie, mistero e pericolo. Si dice che per sopravvivere qui bisogna essere matti come un cappellaio. E per fortuna...io lo sono. "</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | BAGNO: Bagno in comune, | SPAZI ALL'APERTO: Area picnic, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Sdraio/lettini, Piscina con vista, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Disponibilità di camere familiari, Camere non fumatori, | ATTIVITÀ: Tour in bicicletta
+a pagamento, Tour a piedi, Escursioni in bicicletta
+Non sul posto, Escursionismo
+Non sul posto, Noleggio biciclette (a pagamento), Sci, | ALTRI SERVIZI: Check-in e check-out express, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Accesso con chiavi, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/antica-dimora-campeggio-fiordaliso.it.html</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>antica-dimora-campeggio-fiordaliso</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Resort Orizzonti Glamping</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1081 Via Monte Taccone, 63811 Sant'Elpidio a Mare, Italia</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Set in SantʼElpidio a Mare, Resort Orizzonti Glamping offers accommodation with air conditioning and access to a garden with an outdoor swimming pool.
+There is a fully equipped private bathroom with shower and a hairdryer.
+The tented camp provides a barbecue.
+San Benedetto del Tronto is 36 km from Resort Orizzonti Glamping, while Sirolo is 31 km away. The nearest airport is Ancona Falconara Airport, 48 km from the accommodation.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>La collocazione sopraelevata garantisce un'incantevole vista sulle colline marchigiane e sugli spazi verdi della Riserva naturale, all'orizzonte  scorgono  i monti Sibillini,  dal  Vettore,alla Sibilla  .Questa vista garantisce riservatezza e tranquillità.Attorno un ampio giardino verde con incantevoli ulivi anche secolari, piscina con vista   e con i suoi 3 appartamenti con ingresso indipendenti 2 tende Glampin di lusso completi di ogni confort, .Rende così  il resort Orizzonti un posto unico e speciale.  Siamo noi tutto lo staff di Resort Orizzonti, a prenderci cura di ogni nostro ospite, che aver così accesso non soltanto a una location di pregio ma a un'esperienza esclusiva .</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: Stazione di ricarica per veicoli elettrici, Parcheggio custodito, | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ACCESSIBILITÀ: Intera unità situata al piano terra, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Aperta tutto l'anno, Sdraio/lettini, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Ingresso indipendente, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Vasca comune (daiyokujo), Intrattenimento serale, Mini club, Escursioni in bicicletta, Noleggio biciclette (a pagamento), Ping-pong, Area giochi, | ALTRI SERVIZI: Sala comune/zona TV, Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
+          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | CUCINA: Cucina in comune, Tavolo da pranzo, Utensili da cucina, Frigorifero, | SERVIZI IN CAMERA: Stand appendiabiti, | ANIMALI: | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Possibilità di pranzo al sacco, Servizio lavanderia, | SERVIZI GENERALI: Area fumatori, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Italiano, | </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-podere-sei-poorte.it.html</t>
+          <t>https://www.booking.com/hotel/it/resort-orizzonti-glamping.it.html</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>camping-podere-sei-poorte</t>
+          <t>resort-orizzonti-glamping</t>
         </is>
       </c>
     </row>
@@ -1147,15 +1150,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Camping Blu Fantasy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lungomare Italia 3B, 60019 Senigallia, Italia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Situato sul lungomare, a 4 km da Senigallia, il Camping Blu Fantasy offre appartamenti a ristorazione indipendente, una piscina all’aperto e un giardino con barbecue. Il WiFi è fruibile gratuitamente nelle aree comuni.
+Tutti gli appartamenti sono dotati di aria condizionata, TV a schermo piatto e angolo cottura con forno e frigorifero. Presentano anche un bagno privato con doccia e bidè.
+I più piccoli apprezzeranno il programma di intrattenimento e l’area giochi a loro dedicati. Tra i servizi troverete inoltre un bar, un minimarket e un ristorante esterno convenzionato con trattamento di mezza pensione e pensione completa.
+Il Camping Villaggio Blu si trova a 15 minuti d’auto da Falconara Marittima e a 30 km da Jesi.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>La data di apertura del Villaggio è prevista dal 1° giugno all'11 settembre 2022 compreso, con tutti i servizi operativi, nel rispetto delle norme governative sulla sicurezza e la salute dei nostri ospiti. 
+La biancheria NON è inclusa nel prezzo del soggiorno. Il kit di biancheria completo da letto e da bagno è valido per l'intero soggiorno ed è da noleggiare su richiesta al momento della prenotazione del soggiorno. Il costo per un kit matrimoniale è di 18 Euro, mentre quello del kit singolo di 11,5 Euro. In alternativa si dovrà utilizzare la propria biancheria dal letto e da bagno.
+Il servizio spiaggia NON è incluso nel prezzo del soggiorno. Vi sono 2 stabilimenti balneari con sabbia aggiunta nelle vicinanze; spiaggia convenzionata "TRILLO 148" a 600 metri oppure spiaggia NON convenzionata "Bahya Blanca"a 150 metri (più piccola e meno attrezzata). Spiaggia libera di ghiaia con fondale sabbioso di fronte a noi, a 50 metri.
+Vi aspettiamo!</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Barbecue, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Aerobica, Cabaret, Intrattenimento serale, Mini club, Staff di animazione, Vasca idromassaggio/jacuzzi, Freccette, Karaoke, Ping-pong, Area giochi, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali satellitari, | SERVIZI DI RISTORAZIONE: Frutta
+a pagamento, Vino/champagne
+a pagamento, Buffet per bambini, Pasti per bambini, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio in strada, | ALTRI SERVIZI: Servizio navetta, Sala comune/zona TV, Servizio navetta (gratuito), Possibilità di pranzo al sacco, Servizio lavanderia
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Cancelletti di sicurezza per bambini, Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | 2 PISCINE: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Zona acqua bassa, Anche per bambini, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/villaggio-camping-blu.it.html</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>villaggio-camping-blu</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Tobacco Road camping Sirolo</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Via Peschiera 9, 60020 Sirolo, Italia</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 18 minuti a piedi dalla spiaggia. Situato a Sirolo, il Tobacco Road camping Sirolo offre una vista sulla sua piscina, un bar, un salotto in comune e sistemazioni con WiFi gratuito.
 Le unità dispongono di patio, cucina con frigorifero, zona pranzo, area soggiorno con TV a schermo piatto e bagno privato con doccia.
@@ -1163,12 +1215,12 @@
 I famosi luoghi di interesse nelle vicinanze del Tobacco Road camping Sirolo includono le spiagge di Urbani, San Michele e Numana. L’Aeroporto di Ancona-Falconara, il più vicino, sorge a 23 km.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | VISTA: Vista piscina, | SPAZI ALL'APERTO: Area picnic, Zona pranzo all'aperto, Barbecue, Patio, | CUCINA: Tavolo da pranzo, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo
 Non sul posto, Happy hour
@@ -1180,61 +1232,14 @@
 a pagamento, | ALTRI SERVIZI: Sala comune/zona TV, Check-in e check-out privati, Possibilità di pranzo al sacco, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Insonorizzazione, Ingresso indipendente, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Recinto attorno alla piscina, Sdraio/lettini, Bar a bordo piscina, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.booking.com/hotel/it/tobacco-road.it.html</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>tobacco-road</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Safaritent Glamping Mar Y Sierrra</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>via S. Gervasio, 61039 Casa Castellani, Italia</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Situato a Casa Castellani, il Safaritent Glamping Mar Y Sierrra offre un ristorante, una piscina stagionale all'aperto e un bar. La struttura dista 37 km da Urbino e dispone di un parcheggio privato gratuito.
-In loco troverete anche un'area giochi per bambini. Durante il vostro soggiorno al Safaritent Glamping Mar Y Sierrra potrete giocare a ping pong in loco o esplorare i dintorni in bicicletta.
-La struttura dista 41 km da Ancona e 27 km da Pesaro. Il Safaritent Glamping Mar Y Sierrra dista 25 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARCHEGGIO: Parcheggio per disabili, | INTERNET: | CUCINA: Utensili da cucina, | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | SPAZI ALL'APERTO: Arredamento da esterni, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Bar a bordo piscina, Ombrelloni, Scivolo d'acqua, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Zanzariera, Parquet o pavimento in legno, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Vino/champagne
-a pagamento, Pasti per bambini, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Snorkeling
-Non sul posto, Equitazione
-Non sul posto, Escursioni in bicicletta
-Non sul posto, Vasca idromassaggio/jacuzzi, Windsurf
-Non sul posto, Ping-pong, Area giochi, Campo da tennis, | ALTRI SERVIZI: Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/safaritent-glamping-mar-y-sierrra.it.html</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>safaritent-glamping-mar-y-sierrra</t>
         </is>
       </c>
     </row>
@@ -1244,15 +1249,59 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Camping Liana</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lungomare Leonardo da Vinci 54 ter, 60019 Senigallia, Italia</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Situato a Senigallia, a 26 km da Ancona, il Camping Liana offre un ristorante e la connessione WiFi gratuita.
+La sistemazione dispone di aria condizionata, TV a schermo piatto, cucina interamente attrezzata con zona pranzo e bagno privato completo di doccia. Potrete usufruire di lenzuola e asciugamani a costo aggiuntivo.
+Presso il campeggio potrete gustare al mattino una colazione all’italiana.
+Il Camping Liana dista 35 km da Sirolo e 44 km da Porto Recanati. L’Aeroporto di Ancona-Falconara, lo scalo più vicino, sorge a 27 km.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista luogo di interesse, Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Spiaggia privata
+a pagamento, | AREA SOGGIORNO: Zona pranzo, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Zanzariera, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-liana.it.html</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>camping-liana</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Camping Norina</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Via Marina Ardizia 181, 61122 Pesaro, Italia</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Ubicato a Pesaro, il Camping Norina vanta un ristorante, un centro fitness e una spiaggia privata, e offre la connessione WiFi gratuita in tutte le aree.
 Tutti gli alloggi sono climatizzati e dotati di TV a schermo piatto e di bagno privato con asciugacapelli.
@@ -1260,42 +1309,85 @@
 La struttura dista 10 minuti di auto da Pesaro e da Fano e 23 km da Cattolica.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Attrezzature per sport acquatici sul posto, Spiaggia privata, Area giochi, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.booking.com/hotel/it/camping-norina.it.html</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>camping-norina</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camping Pineta</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Via ca' mignone 5, 61029 Urbino, Italia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Situato a Urbino, il Camping Pineta offre piscina, ristorante, bar, vista città e WiFi gratuito.
+Le sistemazioni comprendono patio, cucina con frigorifero, zona pranzo, salotto con TV e bagno privato con bidè e asciugacapelli. Per maggiore comodità, potrete usufruire di asciugamani e lenzuola ad un costo aggiuntivo.
+In loco avrete a disposizione una terrazza.
+Il Camping Pineta dista 5 km dal Duomo. L’Aeroporto Internazionale Federico Fellini è lo scalo più vicino, a 57 km dalla struttura.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ll Camping “Pineta” di Urbino è sorto in un'area di circa 22.000 metri quadri a est della citta, situato in una posizione eccellente sia dal punto di vista paesaggistico che da quello funzionale. Infatti si tratta di un terreno in declivio verso la città dal quale si gode un'ottima vista del Centro Storico. ll terreno dove sorge il Camping e in gran parte coperto da una folta pineta dando al campeggiatore uno stretto rapporto con Ia natura e il paesaggio circostante.  I servizi interni del Camping comprendono: bagni, lavandini, Iavelli, lavatoi, docce calde e fredde, fontane e torrette a norme CEE per prese di corrente (220 WT) dislocate in vari punti del terreno, tutto nelle proporzioni previste dalla legge; inoltre funzionano un Bar, un ristorante , piscina e sono disponibili anche bungalow .</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Asciugacapelli, Doccia, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Letto pieghevole, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Patio, Terrazza, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: | SERVIZI GENERALI: Soluzioni anallergiche, Aria condizionata, Zanzariera, Parquet o pavimento in legno, Riscaldamento, Insonorizzazione, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Bar, | ATTIVITÀ: Solarium, | VISTA: Vista luogo di interesse, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-pineta-urbino.it.html</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>camping-pineta-urbino</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Camping Paradiso</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Via Rive Del Faro 2, 61121 Pesaro, Italia</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 12 minuti a piedi dalla spiaggia. Ubicato nel parco regionale di San Bartolo, a 850 metri da Castel di Mezzo, il Camping Paradiso offre una piscina all'aperto e un barbecue.
 I bungalow e gli chalet dispongono di una terrazza con vista sulle montagne, di un'area salotto e, in alcuni casi, di un'angolo cottura e di una TV a schermo piatto.
@@ -1303,87 +1395,107 @@
 Il Camping Paradiso si trova a 12 km da Pesaro, e in auto dista 15 minuti dalla stazione di Cattolica e 25 minuti da Riccione.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>La nostra peculiarità è l'atmosfera familiare unita a servizi di qualità. Da sempre i nostri ospiti possono contare sul nostro aiuto per risolvere ogni problematica ed esigenza. Non è raro trovarsi la sera insieme al bar o ristorante a scambiarci battute come amici di vecchia data. Spesso i rapporti continuano anche dopo le vacanze e le famiglie tornano a trovarci per più anni.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Patio, Terrazza, Giardino, | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Cucina, Frigorifero, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, | ATTIVITÀ: Vasca all'aperto, Escursioni in bicicletta, Escursionismo, Freccette, Ping-pong, Area giochi, Pesca
 a pagamento, Campo da golf (nel raggio di 3 km)
 a pagamento, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Sala comune/zona TV, Deposito bagagli, Fax/fotocopiatrice, Possibilità di pranzo al sacco, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Giochi da tavolo/puzzle, | PROTEZIONE E SICUREZZA: Telecamere a circuito chiuso nelle zone in comune, Cassaforte, | SERVIZI GENERALI: Minimarket sul posto, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Piscina con vista, Piscina di acqua salata, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.booking.com/hotel/it/camping-paradiso.it.html</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>camping-paradiso</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Camping Pineta</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Via ca' mignone 5, 61029 Urbino, Italia</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Situato a Urbino, il Camping Pineta offre piscina, ristorante, bar, vista città e WiFi gratuito.
-Le sistemazioni comprendono patio, cucina con frigorifero, zona pranzo, salotto con TV e bagno privato con bidè e asciugacapelli. Per maggiore comodità, potrete usufruire di asciugamani e lenzuola ad un costo aggiuntivo.
-In loco avrete a disposizione una terrazza.
-Il Camping Pineta dista 5 km dal Duomo. L’Aeroporto Internazionale Federico Fellini è lo scalo più vicino, a 57 km dalla struttura.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ll Camping “Pineta” di Urbino è sorto in un'area di circa 22.000 metri quadri a est della citta, situato in una posizione eccellente sia dal punto di vista paesaggistico che da quello funzionale. Infatti si tratta di un terreno in declivio verso la città dal quale si gode un'ottima vista del Centro Storico. ll terreno dove sorge il Camping e in gran parte coperto da una folta pineta dando al campeggiatore uno stretto rapporto con Ia natura e il paesaggio circostante.  I servizi interni del Camping comprendono: bagni, lavandini, Iavelli, lavatoi, docce calde e fredde, fontane e torrette a norme CEE per prese di corrente (220 WT) dislocate in vari punti del terreno, tutto nelle proporzioni previste dalla legge; inoltre funzionano un Bar, un ristorante , piscina e sono disponibili anche bungalow .</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Asciugacapelli, Doccia, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Letto pieghevole, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Patio, Terrazza, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: | SERVIZI GENERALI: Soluzioni anallergiche, Aria condizionata, Zanzariera, Parquet o pavimento in legno, Riscaldamento, Insonorizzazione, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Bar, | ATTIVITÀ: Solarium, | VISTA: Vista luogo di interesse, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-pineta-urbino.it.html</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>camping-pineta-urbino</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CIVETTUOLA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20 Via Consolazione, 60010 Castel Colonna, Italia</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CIVETTUOLA is situated in Castel Colonna and offers a bar and a terrace. The property is 8 km from Senigallia and free private parking is available.
+Towels and bed linen are provided.
+Guests at the tented camp can enjoy a continental breakfast.
+Guests can swim in the outdoor swimming pool, go hiking or cycling, or relax in the garden and use the barbecue facilities.
+Sirolo is 43 km from CIVETTUOLA, while Ancona is 32 km from the property. The nearest airport is Ancona Falconara Airport, 20 km from the accommodation.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Piccola tenda fissa posizionata nel bordo del parco della struttura principale. Intima, esclusiva, panoramica.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Prodotti per le pulizie, Utensili da cucina, Lavatrice, Frigorifero, | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Servizi igienici in comune, Bagno privato, Doccia, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, | ANIMALI: | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Patio, Balcone, Terrazza, Giardino, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Giochi da piscina, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: Sdraio/lettini, | SERVIZI GENERALI: Ciotole per animali domestici, Ceste per animali domestici, Area fumatori, Ingresso indipendente, Possibilità di pranzo al sacco, Navetta aeroportuale, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Frutta
+a pagamento, Vino/champagne
+a pagamento, Bar, | ATTIVITÀ: Tiro con l'arco, Tour o lezioni sulla cultura locale, Happy hour
+a pagamento, Tour in bicicletta, Tour a piedi, Massaggi corpo
+a pagamento, Massaggi mani
+a pagamento, Massaggi testa
+a pagamento, Massaggi di coppia
+a pagamento, Massaggi piedi
+a pagamento, Massaggi collo
+a pagamento, Massaggi schiena
+a pagamento, Equitazione
+Non sul posto
+a pagamento, Escursioni in bicicletta
+Non sul posto, Escursionismo
+Non sul posto, Massaggi
+a pagamento, Pesca
+Non sul posto, | VISTA: Vista luogo di interesse, Vista giardino, | TRASPORTI: Navetta per l'aeroporto
+a pagamento, Navetta dall'aeroporto
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Check-in e check-out privati, Deposito bagagli, Check-in e check-out express, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | SERVIZI BUSINESS: Fax/fotocopiatrice
+a pagamento, | PROTEZIONE E SICUREZZA: Accesso con chiavi, Sicurezza 24 ore su 24, | LINGUE PARLATE: Inglese, Spagnolo, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/civettuola.it.html</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>civettuola</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Camping Village Costa Verde</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Contrada Asola, 62018 Porto Potenza Picena, Italia</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 3 minuti a piedi dalla spiaggia. Situato a Porto Potenza Picena, a 200 metri dalle spiagge di sabbia, il Camping Village Costa Verde offre una piscina all'aperto, un ristorante e la connessione Wi-Fi gratuita nelle aree comuni.
 La struttura metterà a vostra disposizione una reception aperta 24 ore su 24, programmi di intrattenimento serali e per bambini, un'area TV in comune e alcuni servizi a pagamento, come il noleggio di biciclette o di sedie a sdraio per la spiaggia privata.
@@ -1392,12 +1504,12 @@
 Dotato di parcheggio gratuito, il campeggio dista 11,5 km da Porto Sant'Elpidio e 20 minuti di auto dal punto di inizio del Parco Regionale del Conero.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Il Camping Village Costa Verde si trova nelle Marche, a pochi chilometri da una delle aree più suggestive della splendida riviera Adriatica, il Parco naturale del Conero.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Intrattenimento serale, Attrezzature per sport acquatici sul posto
 a pagamento, Staff di animazione, Spiaggia privata
@@ -1409,107 +1521,14 @@
 a pagamento, Riscaldamento, Disponibilità di camere familiari, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.booking.com/hotel/it/camping-village-costa-verde.it.html</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>camping-village-costa-verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Camping Liana</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Lungomare Leonardo da Vinci 54 ter, 60019 Senigallia, Italia</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Situato a Senigallia, a 26 km da Ancona, il Camping Liana offre un ristorante e la connessione WiFi gratuita.
-La sistemazione dispone di aria condizionata, TV a schermo piatto, cucina interamente attrezzata con zona pranzo e bagno privato completo di doccia. Potrete usufruire di lenzuola e asciugamani a costo aggiuntivo.
-Presso il campeggio potrete gustare al mattino una colazione all’italiana.
-Il Camping Liana dista 35 km da Sirolo e 44 km da Porto Recanati. L’Aeroporto di Ancona-Falconara, lo scalo più vicino, sorge a 27 km.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista luogo di interesse, Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Spiaggia privata
-a pagamento, | AREA SOGGIORNO: Zona pranzo, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Zanzariera, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | LINGUE PARLATE: Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-liana.it.html</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>camping-liana</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>fattoria country village</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>contrada fonte san giovanni 3 montecarotto contrada fonte san giovanni 3, 60036 Montecarotto, Italia</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Hai diritto a uno sconto Genius su fattoria country village! Per risparmiare su questa struttura ti basta accedere.
-Situato a Montecarotto, nelle Marche, il Fattoria Country Village offre sistemazioni con parcheggio privato gratuito.
-A disposizione un bagno in comune completamente attrezzato con bidet e set di cortesia.
-Al mattino vi attende una colazione a buffet o all'italiana.
-Potrete approfittare di un barbecue e rilassarvi in giardino o nell’area salotto in comune.
-Il Fattoria Country Village dista 45 km da Sirolo e 26 km da Senigallia. A 39 km raggiungerete l’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARCHEGGIO: Parcheggio custodito, | INTERNET: | CUCINA: Cucina in comune, | BAGNO: Carta igienica, Bidet, Vasca o doccia, Servizi igienici in comune, WC, Prodotti da bagno in omaggio, Bagno in comune, Vasca, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Barbecue, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Teli da piscina/spiaggia, Sdraio/lettini, Giochi da piscina, Ombrelloni, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | SERVIZI GENERALI: Ciotole per animali domestici, WiFi a pagamento, Sala comune/zona TV, Servizio navetta (a pagamento), Possibilità di pranzo al sacco, Cappella o luogo di culto, Camere/strutture per ospiti disabili, Cassaforte, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
-a pagamento, Pasti per bambini, Snack bar, | ATTIVITÀ: Tiro con l'arco, Happy hour
-a pagamento, Tour in bicicletta, Tour a piedi
-a pagamento, Giro dei pub
-a pagamento, Attrezzatura da badminton, Vasca all'aperto, Staff di animazione, Escursioni in bicicletta, Ping-pong, Pesca, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Check-in e check-out privati, Reception 24 ore su 24, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | SERVIZI BUSINESS: Fax/fotocopiatrice, | LINGUE PARLATE: Inglese, Spagnolo, | </t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/fattoria-country-village.it.html</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>fattoria-country-village</t>
         </is>
       </c>
     </row>
@@ -1519,46 +1538,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bungalow Verde Mare</t>
+          <t>Glamping Marche Nascoste Tenda e intero alloggio</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lungomare Marina Palmense, 63900 Marina Palmense, Italia</t>
+          <t>41 Strada Provinciale 54, 62020 Penna San Giovanni, Italia</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Offering sea views and a seasonal outdoor swimming pool, Bungalow Verde Mare offers accommodation conveniently located in Marina Palmense, within a short distance of Porto San Giorgio Beach.
-The camping offers a seating area with a flat-screen TV and a private bathroom with a hairdryer and bidet.
-A children's playground is also available for guests at Bungalow Verde Mare.
-The nearest airport is Ancona Falconara Airport, 62 km from the accommodation.</t>
+          <t>Located in Penna San Giovanni in the Marche region, Glamping Marche Nascoste Tenda e intero alloggio features a garden. The property is 39 km from Grottammare and free private parking is provided.
+The tented camp also provides a fully equipped kitchen with a fridge, a seating area, a washing machine and 1 bathroom with a bidet and a bath.
+An Italian breakfast is available daily at the tented camp.
+San Benedetto del Tronto is 41 km from Glamping Marche Nascoste Tenda, while Porto Recanati is 47 km away. The nearest airport is Ancona Falconara Airport, 61 km from the accommodation.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>No camping host description</t>
+          <t>Nel piccolo borgo di Penna San Giovanni potrete soggiornare nella tenda Sibilla ,all'ombra degli alberi del nostro giardino con vista sui Sibillini, tra ulivi e fiori. Tenda di 5 m di diametro arredata (max 4 pers.) e intero alloggio privato con bagno, cucina, una camera (altre 2 pers.), sala e intrattenimento per vivere momenti meravigliosi. L'alloggio può ospitare fino a 6 persone dello stesso nucleo.
+Colazione con prodotti freschi locali. Noleggio bici, trekking, spiagge nelle vicinanze e molto altro!
+La nostra filosofia: green, fai da te, riutilizzo per limitare l'impatto ambientale.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Bidet, Bagno privato, WC, Asciugacapelli, | VISTA: Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Lavatrice, Frigorifero, | SERVIZI IN CAMERA: Divano letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Happy hour
-a pagamento, Spiaggia, Attrezzatura da tennis
-a pagamento, Intrattenimento serale, Locale notturno/DJ, Staff di animazione, Area giochi, Campo da tennis
-a pagamento, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio lavanderia
-a pagamento, Servizio baby-sitter
-a pagamento, | SERVIZI GENERALI: Minimarket sul posto, Ferro e asse da stiro, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Bar a bordo piscina, Ombrelloni, Scivolo d'acqua, | SERVIZI BENESSERE: Ombrelloni
-a pagamento, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Inglese, Italiano, | </t>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Tostapane, Piano cottura, Forno, Utensili da cucina, Cucina, Lavatrice, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Asciugamani, Bidet, Vasca o doccia, Servizi igienici in comune, Bagno privato, WC, Prodotti da bagno in omaggio, Asciugacapelli, Vasca, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | SERVIZI GENERALI: Zanzariera, Pavimento in marmo o in piastrelle, Ingresso indipendente, Riscaldamento, Ventilatore, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Frutta, Vino/champagne
+a pagamento, Possibilità di colazione in camera, Bollitore tè/macchina caffè, | ATTIVITÀ: Freccette, Ping-pong, | ALTRI SERVIZI: Ciotole per animali domestici, Servizio lavanderia, | VISTA: Vista montagna, Vista giardino, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, Giochi da tavolo/puzzle, | LINGUE PARLATE: Tedesco, Inglese, Spagnolo, Italiano, | </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/bungalow-verde-mare.it.html</t>
+          <t>https://www.booking.com/hotel/it/glamping-marche-nascoste-tenda-e-intero-alloggio.it.html</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>bungalow-verde-mare</t>
+          <t>glamping-marche-nascoste-tenda-e-intero-alloggio</t>
         </is>
       </c>
     </row>
@@ -1616,43 +1632,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Glamping Marche Nascoste Tenda e intero alloggio</t>
+          <t>Camping Villaggio Cortina</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>41 Strada Provinciale 54, 62020 Penna San Giovanni, Italia</t>
+          <t>Lungomare Italia 1/1, 60019 Senigallia, Italia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Located in Penna San Giovanni in the Marche region, Glamping Marche Nascoste Tenda e intero alloggio features a garden. The property is 39 km from Grottammare and free private parking is provided.
-The tented camp also provides a fully equipped kitchen with a fridge, a seating area, a washing machine and 1 bathroom with a bidet and a bath.
-An Italian breakfast is available daily at the tented camp.
-San Benedetto del Tronto is 41 km from Glamping Marche Nascoste Tenda, while Porto Recanati is 47 km away. The nearest airport is Ancona Falconara Airport, 61 km from the accommodation.</t>
+          <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Il Camping Villaggio Cortina sorge sul lungomare di Senigallia, proprio di fronte alla spiaggia. Offre la connessione Wi-Fi gratuita nella zona della reception.
+Alcune unità sono dotate di aria condizionata, angolo cottura con frigorifero e zona pranzo.
+La struttura dispone di un bar in loco dove potrete gustare un drink. A vostra disposizione anche una spiaggia privata.
+Il Camping Cortina dista 5 km dalla stazione ferroviaria di Senigallia e 24 km da Ancona.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nel piccolo borgo di Penna San Giovanni potrete soggiornare nella tenda Sibilla ,all'ombra degli alberi del nostro giardino con vista sui Sibillini, tra ulivi e fiori. Tenda di 5 m di diametro arredata (max 4 pers.) e intero alloggio privato con bagno, cucina, una camera (altre 2 pers.), sala e intrattenimento per vivere momenti meravigliosi. L'alloggio può ospitare fino a 6 persone dello stesso nucleo.
-Colazione con prodotti freschi locali. Noleggio bici, trekking, spiagge nelle vicinanze e molto altro!
-La nostra filosofia: green, fai da te, riutilizzo per limitare l'impatto ambientale.</t>
+          <t>Da più di 15 anni ospitiamo famiglie, coppie e campeggiatori nella nostra struttura. 
+Abbiamo piazzole per tende, roulotte e camper e comode mobilhouse da 4 o 5 posti.
+Il nostro pacchetto all-inclusive vi permette di pagare una sola volta per avere tutto ciò che può servirvi, mobilhouse, parcheggio, pulizie animazione e servizio spiaggia tutto compreso!
+Voi dovrete portare soltando la crema solare!</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Tostapane, Piano cottura, Forno, Utensili da cucina, Cucina, Lavatrice, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Asciugamani, Bidet, Vasca o doccia, Servizi igienici in comune, Bagno privato, WC, Prodotti da bagno in omaggio, Asciugacapelli, Vasca, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | SERVIZI GENERALI: Zanzariera, Pavimento in marmo o in piastrelle, Ingresso indipendente, Riscaldamento, Ventilatore, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Frutta, Vino/champagne
-a pagamento, Possibilità di colazione in camera, Bollitore tè/macchina caffè, | ATTIVITÀ: Freccette, Ping-pong, | ALTRI SERVIZI: Ciotole per animali domestici, Servizio lavanderia, | VISTA: Vista montagna, Vista giardino, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, Giochi da tavolo/puzzle, | LINGUE PARLATE: Tedesco, Inglese, Spagnolo, Italiano, | </t>
+          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, | SPAZI ALL'APERTO: Arredamento da esterni, Barbecue, Terrazza, Giardino, | CUCINA: Frigorifero, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ATTIVITÀ: Spiaggia, Intrattenimento serale, Fronte spiaggia, Staff di animazione, Spiaggia privata, Windsurf
+Non sul posto
+a pagamento, Ping-pong, | SERVIZI DI RISTORAZIONE: Pasti per bambini
+a pagamento, Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | TRASPORTI: Biglietti per i mezzi di trasporto, | ALTRI SERVIZI: Servizio navetta, Servizio lavanderia
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Estintori, Accesso con chiavi, | SERVIZI GENERALI: Aria condizionata, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Lavabo più basso, WC con maniglioni, Accesso su sedia a rotelle, | SERVIZI BENESSERE: Ombrelloni, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/glamping-marche-nascoste-tenda-e-intero-alloggio.it.html</t>
+          <t>https://www.booking.com/hotel/it/villaggio-cortina.it.html</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>glamping-marche-nascoste-tenda-e-intero-alloggio</t>
+          <t>villaggio-cortina</t>
         </is>
       </c>
     </row>

--- a/datasets/general_data_dataset_booking.xlsx
+++ b/datasets/general_data_dataset_booking.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,52 +471,54 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CAMPING TRE ARCHI</t>
+          <t>Natural Village Resort</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>via ugo la malfa 19/A, 63900 Lido di Fermo, Italia</t>
+          <t>Contrada Torrenova 1 SS 16 Km 331,48, 62018 Porto Potenza Picena, Italia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hai diritto a uno sconto Genius su CAMPING TRE ARCHI! Per risparmiare su questa struttura ti basta accedere.
-Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Situato a Lido di Fermo, a 25 km da Porto Recanati, il CAMPING TRE ARCHI offre un ristorante e il WiFi gratuito.
-L’alloggio dispone di aria condizionata, cucina completamente accessoriata, TV a schermo piatto e bagno privato con bidet. Lenzuola e asciugamani sono fruibili a un costo aggiuntivo.
-Al mattino vi attende una colazione italiana.
-Il CAMPING TRE ARCHI ospita anche una terrazza.
-Potrete usufruire di un giardino con barbecue in loco e praticare il ciclismo nei dintorni.
-La struttura dista 36 km da Sirolo e 39 km da San Benedetto del Tronto. Il CAMPING TRE ARCHI si trova a 63 km dall’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
+          <t>Hai diritto a uno sconto Genius su Natural Village Resort! Per risparmiare su questa struttura ti basta accedere.
+Situato a Porto Potenza Picena, lungo la Riviera del Conero, il Natural Village Resort offre una spiaggia privata e una piscina. A disposizione troverete moderni chalet dotati di una veranda attrezzata con tavoli e sedie.
+Gli appartamenti sono distribuiti su 6 ettari di terreno e includono aria condizionata, TV, angolo cottura e bagno. Usufruirete inoltre di 1 posto auto.
+In loco apprezzerete anche le strutture sportive e l’intrattenimento per adulti e bambini.
+Ubicato di fronte alla spiaggia, a 4 km da Porto Recanati e a 20 minuti di auto da Numana e Marcelli, il Natural Village Resort dispone di un campo da tennis.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I  bungalow si trovano sulla riviera fermana,direttamente sulla spiaggia,lontano dalla ferrovia o strade rumorosee immerso nel verde pioppeto del camping Tre Archi.l trilocali sono di nuova costruzione dotato di tutti i confort  e hanno il posto auto privato davanti alla struttura.Il posto è adatto alla famiglia con figli per la presenza di parco giochi,campo di pallone,pallacanestro,bocce,ping pong,animazione serale,miniclub per bambini ,aria condizionata,barbecue,nessuna strada d'attraversare per la spiaggia,possibilità di affittare biciclette ed attrezzatura da spiaggia.wi-fi gratuito.
-Adiacente alla struttura passa una lunga pista ciclabile che unisce Porto San Giorgio e Porto Sant' Elpidio.Nelle vicinanze: piscina,supermarket,ristoranti,pizzerie,stabilimenti attrezzati,
-piccoli borghi medievali,outlet e spacci aziendali  di calzature di firme  prestigiose.
-:</t>
+          <t>No camping host description</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Arredamento da esterni, Barbecue, Barbecue, Terrazza, Giardino, | CUCINA: Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Escursioni in bicicletta
-Non sul posto, Escursionismo
-Non sul posto, Ping-pong, Pesca
-Non sul posto, | AREA SOGGIORNO: Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | SERVIZI GENERALI: Aria condizionata
-a pagamento, Pavimento in marmo o in piastrelle, Ingresso indipendente, Riscaldamento, Disponibilità di camere familiari, | ACCESSIBILITÀ: Intera unità situata al piano terra, | SERVIZI BENESSERE: Ombrelloni
-a pagamento, Sdraio/lettini
-a pagamento, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Rumeno, | </t>
+          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, Vista mare, | SPAZI ALL'APERTO: Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Patio, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, | ANIMALI: | ATTIVITÀ: Aerobica, Tiro con l'arco, Spettacolo/musica dal vivo, Happy hour, Tour in bicicletta
+a pagamento, Cabaret, Spiaggia, Lezioni di fitness, Lezioni di yoga, Fitness, Attrezzatura da tennis
+a pagamento, Intrattenimento serale, Fronte spiaggia, Mini club, Attrezzature per sport acquatici sul posto
+a pagamento, Staff di animazione, Spiaggia privata
+a pagamento, Minigolf, Canoa
+a pagamento, Windsurf
+a pagamento, Karaoke, Ping-pong, Area giochi, Campo da golf (nel raggio di 3 km)
+a pagamento, Campo da tennis, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali satellitari, TV, | SERVIZI DI RISTORAZIONE: Frutta
+a pagamento, Vino/champagne
+a pagamento, Pasti per bambini
+a pagamento, Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio pulizie giornaliero
+a pagamento, Deposito bagagli, Fax/fotocopiatrice, Servizio lavanderia
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, Cassaforte, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Zanzariera, Riscaldamento, Insonorizzazione, Ingresso indipendente, Disponibilità di camere familiari, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Recinto attorno alla piscina, Teli da piscina/spiaggia, Sdraio/lettini, Bar a bordo piscina, Giochi da piscina, Ombrelloni, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni
+a pagamento, Sdraio/lettini, Teli da piscina/spiaggia, | LINGUE PARLATE: Tedesco, Inglese, Spagnolo, Francese, Italiano, | </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-tre-archi.it.html</t>
+          <t>https://www.booking.com/hotel/it/nuovo-natural-village.it.html</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>camping-tre-archi</t>
+          <t>nuovo-natural-village</t>
         </is>
       </c>
     </row>
@@ -526,50 +528,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camping La Pineta</t>
+          <t>La Risacca Family Camping Village</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Via della repubblica 3, 62017 Porto Recanati, Italia</t>
+          <t>Via Europa 100, 63821 Porto SantʼElpidio, Italia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Situato nella località marchigiana di Porto Recanati, a 25 km da Ancona e a 49 km da Senigallia, il Camping La Pineta vanta un'area giochi per bambini, una spiaggia privata e servizi gratuiti quali la connessione WiFi e un parcheggio privato in loco.
-Alcune sistemazioni dispongono di aria condizionata, di zona pranzo e/o di patio, e su richiesta potrete usufruire di una TV. Avrete a disposizione anche un angolo cottura con frigorifero e fornelli e un bagno privato con vasca o doccia e bidè.
-In loco sono presenti un ristorante e un minimarket.
-Presso la struttura potrete giocare a ping pong e noleggiare biciclette. Il Camping La Pineta dista 13 km da Civitanova Marche e 33 km dall'Aeroporto di Ancona Falconara, il più vicino alla struttura.</t>
+          <t>Situato a Fonte di Mare, lungo il Mare Adriatico, il Centro Vacanze La Risacca offre un parco acquatico gratuito con piscina all'aperto, un campo da tennis, una spiaggia riservata, un miniclub e un ristorante.
+Le sistemazioni presentano un angolo cottura, una zona giorno, una TV e un bagno privato con doccia.
+In loco troverete un ristorante alla carta e un minimarket fornito di vari generi alimentari.
+Tra le attività e i servizi disponibili figurano un ping pong, una vasca idromassaggio, biciclette a noleggio e un'area giochi per bambini. Avrete inoltre modo di praticare varie attività, quali il windsurf, il canoismo e il ciclismo.
+Provvisto di un parcheggio privato gratuito, il Centro Vacanze La Risacca dista 5 minuti in auto da Civitanova Marche.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Situato in posizione peculiare direttamente sul mare il Camping Pineta offre al proprio ospite un soggiorno di relax e divertimento. A sud di Porto Recanati, a solo 800 mt dal centro del paese, facilmente raggiungibile tramite  una passeggiata pedonale. A pochi passi dalla rinomata Riviera del Conero e da zone di interesse culturale come Loreto e Recanati. All'interno si potra' trovare bar, ristorante, pizzeria, minimarket, noleggio bici, navetta per il centro e animazione serale e diurna dal 01/07. Cani di piccola taglia ammessi</t>
+          <t>Il Centro Vacanze è un'ottima soluzione per chi vuole trascorrere una vacanza insieme alla propria famiglia. I bambini possono divertirsi e muoversi in assoluta libertà e sicurezza ma anche per gli adulti le attività non mancano davvero!</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAGNO: Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Tour o lezioni sulla cultura locale
-a pagamento, Happy hour
-a pagamento, Serate con cene a tema, Tour in bicicletta
-a pagamento, Serate di cinema, Cabaret, Spiaggia, Lezioni di fitness, Intrattenimento serale, Fronte spiaggia, Mini club, Staff di animazione, Spiaggia privata
-a pagamento, Escursioni in bicicletta
-Non sul posto, Karaoke, Ping-pong, Area giochi, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: Canali via cavo, TV, | SERVIZI DI RISTORAZIONE: Bar, Ristorante, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio navetta (a pagamento), Servizio navetta (gratuito), Check-in e check-out privati, Fax/fotocopiatrice
-a pagamento, Servizio lavanderia
-a pagamento, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi magnetiche, Accesso con chiavi, Cassaforte, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata
-a pagamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, | SERVIZI BENESSERE: Ombrelloni
-a pagamento, Sdraio/lettini
-a pagamento, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
+          <t xml:space="preserve">BAGNO: Bagno privato, | SPAZI ALL'APERTO: Barbecue, Giardino, | ANIMALI: | ATTIVITÀ: Bingo
+Non sul posto
+a pagamento, Aerobica, Tiro con l'arco
+a pagamento, Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Serate di cinema
+Non sul posto, Cabaret, Spiaggia, Lezioni di fitness, Attrezzatura da tennis, Parco acquatico, Intrattenimento serale, Fronte spiaggia, Mini club, Attrezzature per sport acquatici sul posto
+a pagamento, Staff di animazione, Spiaggia privata
+a pagamento, Equitazione
+Non sul posto
+a pagamento, Escursioni in bicicletta, Escursionismo
+Non sul posto
+a pagamento, Canoa
+a pagamento, Windsurf
+a pagamento, Ping-pong, Area giochi, Solarium, Campo da tennis
+a pagamento, | SERVIZI DI RISTORAZIONE: Pasti per bambini
+a pagamento, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio in strada, | ALTRI SERVIZI: Ciotole per animali domestici, Passeggini, Sala comune/zona TV, Sportello bancomat, Fax/fotocopiatrice
+a pagamento, Possibilità di pranzo al sacco, Servizio lavanderia
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Allarme di sicurezza, Accesso con chiavi, Cassaforte, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Riscaldamento, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: WC con maniglioni, Accesso su sedia a rotelle, | 2 PISCINE: Stagionale, Accessibile a ogni età, Sdraio/lettini, Giochi da piscina, Ombrelloni, Scivolo d'acqua, Zona acqua bassa, Stagionale, Solo per adulti, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Tedesco, Inglese, Spagnolo, Francese, Italiano, | </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-la-pineta.it.html</t>
+          <t>https://www.booking.com/hotel/it/centro-vacanze-la-risacca.it.html</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>camping-la-pineta</t>
+          <t>centro-vacanze-la-risacca</t>
         </is>
       </c>
     </row>
@@ -579,55 +588,58 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saecula Natural Village Experience</t>
+          <t>Girasole Eco Family Village</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contrada Ripacorvara, 1, 63086 Force, Italia</t>
+          <t>SS Adriatica, Località Marina Palmense, 63900 Marina Palmense, Italia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hai diritto a uno sconto Genius su Saecula Natural Village Experience! Per risparmiare su questa struttura ti basta accedere.
-Situato a Force, il Saecula Natural Village Experience offre la connessione WiFi gratuita e suite dotate di cucina, area salotto e TV a schermo piatto.
-La nostra è una struttura Agrituristica composta da: ALLOGGI (Appartamenti - Suite Familiare. I nostri quattro moderni appartamenti consentono un sereno soggiorno nel verde caratteristico del nostro villaggio naturale a ridosso del nostro mozzafiato parco di ciliegi); AGRICAMPEGGIO (all’ombra di un vasto ciliegieto, il nostro campeggio dispone di 16 piazzole di 72 mq l’una, disposte in modo da non far mancare spazio e privacy).
-Ogni appartamento dispone di forno, frigorifero, macchina da caffè, piano cottura e bollitore. Alcune unità abitative presentano una zona pranzo e/o una terrazza.
-Gli appartamenti offrono l'accesso a una piscina all'aperto e terrazzini esterni. In loco troverete anche un percorso fitness di 8 stazioni. In loco potrete noleggiare tende, stuoie e sacchi a pelo, e noleggiare gratuitamente le biciclette.
-San Benedetto. La struttura dista 46 km da Del Tronto e 25 km da Ascoli Piceno. L'Aeroporto più vicino è quello di Ancona Falconara, a 116 km da Saecula Natural Village Experience.</t>
+          <t>Situato a Marina Palmense, in una posizione fronte mare, il Girasole Eco Family Village offre servizi a pagamento quali una piscina all'aperto, una vasca idromassaggio e una spiaggia privata.
+Le unità presentano l'aria condizionata, un patio, un angolo cottura ben attrezzato, una TV LCD e un bagno privato con doccia.
+Il Girasole mette a vostra disposizione un piccolo negozio di alimentari, una biblioteca e un ristorante di cucina italiana tradizionale in loco.
+ Il Girasole Eco Family Village vanta anche un'area giochi per bambini, il servizio di noleggio biciclette e un bar che serve drink.
+In loco potrete giocare a tennis e a ping pong, mentre la zona circostante è rinomata per l'escursionismo. La struttura dista 23 km da San Benedetto del Tronto e 30 minuti d'auto da Loreto.
+Il Girasole Eco Family Village sorge a 72 km dall'Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>L'Agriturismo, (nuovo) attivo dal 2018,  è composto da:
--ALLOGGI - (Appartamenti)
-I nostri quattro moderni alloggi consentono un sereno soggiorno nel verde caratteristico del nostro villaggio naturale a ridosso del nostro mozzafiato parco di ciliegi,
-Un'esperienza rilassante senza dover rinunciare alle comodità di un appartamento curato, elegante e allo stesso tempo tradizionale.
-Gli alloggi, adatti dalle 2 alle 4/5 persone, possono ospitare sia coppie, che famiglie, senza rinunciare a spazi ampi, offrono, compresi nel servizio: 
-- piscina esterna; solarium;  terrazzino; Wi-Fi free; cucina attrezzata; tv satellitare; riscaldamento autonomo; aria condizionata.
--AGRI CAMPEGGIO (Piazzole)
-All’ombra di un vasto ciliegieto, il nostro campeggio dispone di n. 16  piazzole di 72 mq l’una, disposte in modo da non far mancare spazio e privacy.
-L’illuminazione serale e notturna garantisce una luminosità efficace ma non invasiva, per godere del fascino protagonista della natura che circonda. 
-Inoltre tutti gli ospiti della nostra struttura possono fruire, gratuitamente,  su richiesta, in base alla disponibilità ,limitatamente al periodo del soggiorno, di:
-- tende + stuoie + sacco a pelo.</t>
+          <t>Se per la tua vacanza stai cercando un luogo che realizzi i sogni di tutta la famiglia, allora il Girasole Eco Family Village, in località Marina Palmense, a  Fermo, nelle Marche è la scelta giusta! Un villaggio dove mare e natura si incontrano, dove l’azzurro dell’acqua abbraccia il verde del paesaggio circostante, in una posizione strategica dalla quale sarà facilmente raggiungibile tutto il territorio circostante e i luoghi di maggiore attrazione della regione. Comfort, tranquillità, benessere...ma anche divertimento e sport per tutti: questi sono gli ingredienti della vostra vacanza eco sostenibile al Girasole! Scegliere il Girasole significa concedersi il lusso di vivere mille vacanze in una indimenticabile esperienza!</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bidet, Servizi igienici aggiuntivi, Vasca o doccia, Prodotti da bagno in omaggio, Asciugacapelli, | VISTA: Vista cortile interno, Vista luogo di interesse, Vista montagna, Vista giardino, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | CUCINA: Prodotti per le pulizie, Lavatrice, | ANIMALI: | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Mostre d'arte temporanee
-Non sul posto, Fitness, Vasca all'aperto, Escursioni in bicicletta, Escursionismo, Ping-pong, Solarium, Palestra, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | ALTRI SERVIZI: Armadietti, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Check-in e check-out privati, Sportello bancomat, Deposito bagagli, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Giochi da tavolo/puzzle, Libri, DVD o musica per bambini, Giochi da tavolo/puzzle, Copriprese di sicurezza per bambini, | SERVIZI DI PULIZIA: Servizio pulizie giornaliero
+          <t xml:space="preserve">BAGNO: Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Asciugacapelli, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Patio, Terrazza, Giardino, | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ATTIVITÀ: Aerobica, Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Tour o lezioni sulla cultura locale, Happy hour
+a pagamento, Serate con cene a tema, Tour a piedi, Cabaret, Mostre d'arte temporanee
+Non sul posto, Spiaggia, Lezioni di fitness, Lezioni di yoga, Fitness, Massaggi corpo
+a pagamento, Massaggi mani
+a pagamento, Massaggi piedi
+a pagamento, Massaggi collo
+a pagamento, Massaggi schiena
+a pagamento, Pacchetti spa/benessere, Pediluvio, Sala spa/area relax, Servizi spa, Scrub corpo, Trattamenti corpo, Acconciature, Tinta capelli, Taglio capelli, Pedicure, Manicure, Trattamenti capelli, Servizi di make up, Depilazione con ceretta, Trattamenti viso, Servizi di bellezza, Vasca all'aperto, Intrattenimento serale, Fronte spiaggia, Mini club, Attrezzature per sport acquatici sul posto
+a pagamento, Staff di animazione, Spiaggia privata
+a pagamento, Escursionismo, Canoa
+a pagamento, Vasca idromassaggio/jacuzzi
+a pagamento, Freccette, Karaoke, Ping-pong, Area giochi, Massaggi
+a pagamento, Solarium
+a pagamento, Sala giochi, Palestra, Campo da tennis, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Frutta, Vino/champagne, Pasti per bambini, Menù per diete particolari (su richiesta), Snack bar, Possibilità di colazione in camera, Bar, Ristorante, Bollitore tè/macchina caffè, | INTERNET: | PARCHEGGIO: Stazione di ricarica per veicoli elettrici, | TRASPORTI: Biglietti per i mezzi di trasporto, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Deposito bagagli, Reception 24 ore su 24, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, Servizio baby-sitter
+a pagamento, | SERVIZI DI PULIZIA: Servizio stireria
 a pagamento, Servizio lavanderia
-a pagamento, | PROTEZIONE E SICUREZZA: Estintori, Accesso con chiavi, | SERVIZI GENERALI: Ciotole per animali domestici, Ceste per animali domestici, Minimarket sul posto, Area fumatori, Aria condizionata, Camera anallergica, Riscaldamento, Possibilità di pranzo al sacco, Cappella o luogo di culto, Disponibilità di camere insonorizzate, Disponibilità di camere familiari, Parrucchiere/salone di bellezza, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
+a pagamento, | SERVIZI BUSINESS: Fax/fotocopiatrice, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Ciotole per animali domestici, Minimarket sul posto, Sala comune/zona TV, Soluzioni anallergiche, Aria condizionata, Riscaldamento, Ingresso indipendente, Possibilità di pranzo al sacco, Disponibilità di camere familiari, Parrucchiere/salone di bellezza, Camere/strutture per ospiti disabili, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/saecula.it.html</t>
+          <t>https://www.booking.com/hotel/it/girasole-camping-village.it.html</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>saecula</t>
+          <t>girasole-camping-village</t>
         </is>
       </c>
     </row>
@@ -637,46 +649,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fattoria country village</t>
+          <t>Green Garden Village</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contrada fonte san giovanni 3 montecarotto contrada fonte san giovanni 3, 60036 Montecarotto, Italia</t>
+          <t>Via Peschiera, 3, 60020 Sirolo, Italia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hai diritto a uno sconto Genius su fattoria country village! Per risparmiare su questa struttura ti basta accedere.
-Situato a Montecarotto, nelle Marche, il Fattoria Country Village offre sistemazioni con parcheggio privato gratuito.
-A disposizione un bagno in comune completamente attrezzato con bidet e set di cortesia.
-Al mattino vi attende una colazione a buffet o all'italiana.
-Potrete approfittare di un barbecue e rilassarvi in giardino o nell’area salotto in comune.
-Il Fattoria Country Village dista 45 km da Sirolo e 26 km da Senigallia. A 39 km raggiungerete l’Aeroporto di Ancona-Falconara, lo scalo più vicino.</t>
+          <t>Questa struttura si trova a 12 minuti a piedi dalla spiaggia. Situato a Sirolo, all'interno del Parco Regionale del Conero, il Green Garden Village offre una spiaggia privata con 1 ombrellone e 2 lettini a camera. Potrete usufruire di una piscina all’aperto e di un barbecue.
+Il Green Garden dista 1 km dal Mare Adriatico e 25 minuti di auto da Ancona. In loco è disponibile un parcheggio gratuito.
+Le sistemazioni includono un patio coperto. Le case mobili presentano 1 o 2 camere da letto, una cucina e un bagno con doccia. I monolocali comprendono una zona giorno con angolo cottura, un letto matrimoniale e un letto singolo su un soppalco.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No camping host description</t>
+          <t>Per tutti coloro che scelgono il Green Garden Village per le loro vacanze, mettiamo a disposizione la nostra decennale esperienza nell'ospitalità e la passione per un lavoro che si tramanda da generazioni e che viene condiviso con uno staff preparato ed attento alle esigenze dei nostri ospiti.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: Parcheggio custodito, | INTERNET: | CUCINA: Cucina in comune, | BAGNO: Carta igienica, Bidet, Vasca o doccia, Servizi igienici in comune, WC, Prodotti da bagno in omaggio, Bagno in comune, Vasca, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ACCESSIBILITÀ: Campanello di emergenza nel bagno, Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, | SPAZI ALL'APERTO: Camino all'aperto, Area picnic, Barbecue, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Teli da piscina/spiaggia, Sdraio/lettini, Giochi da piscina, Ombrelloni, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | SERVIZI GENERALI: Ciotole per animali domestici, WiFi a pagamento, Sala comune/zona TV, Servizio navetta (a pagamento), Possibilità di pranzo al sacco, Cappella o luogo di culto, Camere/strutture per ospiti disabili, Cassaforte, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
-a pagamento, Pasti per bambini, Snack bar, | ATTIVITÀ: Tiro con l'arco, Happy hour
-a pagamento, Tour in bicicletta, Tour a piedi
-a pagamento, Giro dei pub
-a pagamento, Attrezzatura da badminton, Vasca all'aperto, Staff di animazione, Escursioni in bicicletta, Ping-pong, Pesca, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Check-in e check-out privati, Reception 24 ore su 24, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | SERVIZI BUSINESS: Fax/fotocopiatrice, | LINGUE PARLATE: Inglese, Spagnolo, | </t>
+          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza, Terrazza solarium, Barbecue, Barbecue, Patio, Giardino, | CUCINA: Frigorifero, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Happy hour
+a pagamento, Spiaggia, Attrezzatura da tennis, Spiaggia privata, Snorkeling
+Non sul posto
+a pagamento, Equitazione
+Non sul posto
+a pagamento, Immersioni subacquee
+Non sul posto
+a pagamento, Escursioni in bicicletta
+Non sul posto, Escursionismo
+Non sul posto
+a pagamento, Canoa
+Non sul posto
+a pagamento, Windsurf
+Non sul posto
+a pagamento, Ping-pong, Area giochi, Pesca
+Non sul posto, Campo da golf (nel raggio di 3 km)
+a pagamento, Campo da tennis
+a pagamento, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali via cavo, TV, | SERVIZI DI RISTORAZIONE: Pasti per bambini
+a pagamento, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Stazione di ricarica per veicoli elettrici, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Deposito bagagli, Banco escursioni, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | SERVIZI DI PULIZIA: Servizio lavanderia
+a pagamento, | SERVIZI BUSINESS: Fax/fotocopiatrice
+a pagamento, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Accesso con chiavi, | SERVIZI GENERALI: Sala comune/zona TV, Servizio navetta (a pagamento), Servizio navetta (gratuito), Area fumatori, Aria condizionata
+a pagamento, Struttura interamente non fumatori, Ingresso indipendente, Possibilità di pranzo al sacco, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Ombrelloni, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/fattoria-country-village.it.html</t>
+          <t>https://www.booking.com/hotel/it/green-garden-village.it.html</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>fattoria-country-village</t>
+          <t>green-garden-village</t>
         </is>
       </c>
     </row>
@@ -686,44 +712,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camping Led Zeppelin</t>
+          <t>Camping Blu Fantasy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5 Contrada Boccabianca, 63064 Cupra Marittima, Italia</t>
+          <t>Lungomare Italia 3B, 60019 Senigallia, Italia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Situato a Cupra Marittima, il Camping Led Zeppelin offre una vista sul proprio giardino, un ristorante, il servizio in camera, un bar, una piscina all’aperto stagionale e un’area giochi per bambini.
-Gli alloggi dispongono di aria condizionata, terrazza, TV a schermo piatto e bagno privato con doccia e set di cortesia. Alcune sistemazioni includono una cucina con microonde e piano cottura.
-In loco è presente un miniclub.
-Il Camping Led Zeppelin dista 10 km da San Benedetto del Tronto e 46 km da Porto Recanati. L’Aeroporto d’Abruzzo, lo scalo più vicino, è ubicato a 73 km.</t>
+          <t>Situato sul lungomare, a 4 km da Senigallia, il Camping Blu Fantasy offre appartamenti a ristorazione indipendente, una piscina all’aperto e un giardino con barbecue. Il WiFi è fruibile gratuitamente nelle aree comuni.
+Tutti gli appartamenti sono dotati di aria condizionata, TV a schermo piatto e angolo cottura con forno e frigorifero. Presentano anche un bagno privato con doccia e bidè.
+I più piccoli apprezzeranno il programma di intrattenimento e l’area giochi a loro dedicati. Tra i servizi troverete inoltre un bar, un minimarket e un ristorante esterno convenzionato con trattamento di mezza pensione e pensione completa.
+Il Camping Villaggio Blu si trova a 15 minuti d’auto da Falconara Marittima e a 30 km da Jesi.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>No camping host description</t>
+          <t>La data di apertura del Villaggio è prevista dal 1° giugno all'11 settembre 2022 compreso, con tutti i servizi operativi, nel rispetto delle norme governative sulla sicurezza e la salute dei nostri ospiti. 
+La biancheria NON è inclusa nel prezzo del soggiorno. Il kit di biancheria completo da letto e da bagno è valido per l'intero soggiorno ed è da noleggiare su richiesta al momento della prenotazione del soggiorno. Il costo per un kit matrimoniale è di 18 Euro, mentre quello del kit singolo di 11,5 Euro. In alternativa si dovrà utilizzare la propria biancheria dal letto e da bagno.
+Il servizio spiaggia NON è incluso nel prezzo del soggiorno. Vi sono 2 stabilimenti balneari con sabbia aggiunta nelle vicinanze; spiaggia convenzionata "TRILLO 148" a 600 metri oppure spiaggia NON convenzionata "Bahya Blanca"a 150 metri (più piccola e meno attrezzata). Spiaggia libera di ghiaia con fondale sabbioso di fronte a noi, a 50 metri.
+Vi aspettiamo!</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Prodotti da bagno in omaggio, Doccia, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Arredamento da esterno, Terrazza, Giardino, | CUCINA: Frigorifero, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Serate di cinema, Cabaret, Spiaggia, Lezioni di fitness, Intrattenimento serale, Fronte spiaggia, Mini club, Locale notturno/DJ, Staff di animazione, Spiaggia privata
-a pagamento, Karaoke, Area giochi, Pesca, Campo da tennis
-a pagamento, | AREA SOGGIORNO: Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
-a pagamento, Pasti per bambini, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | TRASPORTI: Biglietti per i mezzi di trasporto
-a pagamento, | ALTRI SERVIZI: Servizio lavanderia, Servizio in camera, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Allarme di sicurezza, Sicurezza 24 ore su 24, | SERVIZI GENERALI: WiFi a pagamento, Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, Ascensore, Disponibilità di camere familiari, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
+          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Barbecue, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Aerobica, Cabaret, Intrattenimento serale, Mini club, Staff di animazione, Vasca idromassaggio/jacuzzi, Freccette, Karaoke, Ping-pong, Area giochi, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali satellitari, | SERVIZI DI RISTORAZIONE: Frutta
+a pagamento, Vino/champagne
+a pagamento, Buffet per bambini, Pasti per bambini, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio in strada, | ALTRI SERVIZI: Servizio navetta, Sala comune/zona TV, Servizio navetta (gratuito), Possibilità di pranzo al sacco, Servizio lavanderia
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Cancelletti di sicurezza per bambini, Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | 2 PISCINE: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Zona acqua bassa, Anche per bambini, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-led-zeppelin.it.html</t>
+          <t>https://www.booking.com/hotel/it/villaggio-camping-blu.it.html</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>camping-led-zeppelin</t>
+          <t>villaggio-camping-blu</t>
         </is>
       </c>
     </row>
@@ -733,20 +761,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>La Bolla del Borgo. Le Marche tra le stelle.</t>
+          <t>Centro Vacanze - Garden River</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Via Olmigrandi 72, 60013 Corinaldo, Italia</t>
+          <t>Via Ottorino Respighi, 63824 Altidona, Italia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Situato a Corinaldo, nelle Marche, il campeggio La Bolla del Borgo. Le Marche tra le stelle. offre un giardino. Dotata di un parcheggio privato gratuito, la struttura si trova a 37 km da Ancona.
-Potrete usufruire di lenzuola e asciugamani.
-Il campeggio serve una colazione all'italiana o senza glutine.
-Il Bolla del Borgo. Le Marche tra le stelle. dista 49 km da Riccione e 48 km da Sirolo. L’Aeroporto di Ancona-Falconara è lo scalo più vicino e sorge a 24 km.</t>
+          <t>Situato a soli 10 minuti a piedi dalla spiaggia di Marina di Altidona.Il Centro Vacanze - Garden River offre bungalow con patio, una piscina all'aperto e un programma di intrattenimento durante l'estate.
+Il River Garden propone specialità locali e internazionali.Il ristorante è aperto tutti i giorni. Su richiesta, potrete gustare la colazione al bar.
+I bungalow dispongono di area salotto/zona pranzo, angolo cottura attrezzato e pavimenti piastrellati.
+Alcune unità sono dotate di bagno privato, mentre altre sono in comune.
+A soli 1 km troverete bar e ristoranti. L'uscita Pedaso dell'autostrada A14 dista 300 m dalla struttura. Il centro di Altidona è raggiungibile in 10 minuti di auto.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -756,17 +785,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Doccia, | SPAZI ALL'APERTO: Arredamento da esterno, Giardino, | SERVIZI GENERALI: Camere non fumatori, | ALTRI SERVIZI: Check-in e check-out privati, Check-in e check-out express, | VISTA: Vista, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | LINGUE PARLATE: Inglese, Francese, Italiano, Giapponese, | </t>
+          <t xml:space="preserve">BAGNO: Bagno privato, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Terrazza solarium, Terrazza, Giardino, | ANIMALI: | ATTIVITÀ: Aerobica, Trasmissione di eventi sportivi in diretta, Lezioni di cucina, Tour o lezioni sulla cultura locale, Serate con cene a tema
+a pagamento, Tour a piedi, Cabaret, Spiaggia, Lezioni di fitness, Fitness, Intrattenimento serale, Mini club, Staff di animazione, Noleggio biciclette (a pagamento), Freccette, Karaoke, Ping-pong, Area giochi, Solarium, Sala giochi, Pesca
+Non sul posto
+a pagamento, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Frutta
+a pagamento, Vino/champagne
+a pagamento, Buffet per bambini, Pasti per bambini
+a pagamento, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, Parcheggio custodito, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Check-in e check-out privati, Deposito bagagli, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, | SERVIZI DI PULIZIA: Servizio lavanderia
+a pagamento, | SERVIZI BUSINESS: Fax/fotocopiatrice, | PROTEZIONE E SICUREZZA: Estintori, Accesso con chiavi, | SERVIZI GENERALI: Sala comune/zona TV, Servizio navetta (a pagamento), Possibilità di pranzo al sacco, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | 2 PISCINE: Stagionale, Orari di apertura, Anche per bambini, Recinto attorno alla piscina, Sdraio/lettini, Ombrelloni, Piscina a sfioro, Vasca immersione ad acqua fredda, Piscina con vista, Zona acqua bassa, Stagionale, Orari di apertura, Solo per adulti, Recinto attorno alla piscina, Sdraio/lettini, Ombrelloni, Piscina a sfioro, Vasca immersione ad acqua fredda, Piscina con vista, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Spagnolo, Italiano, | </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona.it.html</t>
+          <t>https://www.booking.com/hotel/it/garden-river.it.html</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona</t>
+          <t>garden-river</t>
         </is>
       </c>
     </row>
@@ -776,156 +812,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camping Terrazzo sul mare</t>
+          <t>Camping Village Mar y Sierra</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Via Adriatica nord 109, 63064 Cupra Marittima, Italia</t>
+          <t>Strada San Gervasio 3, 61039 San Costanzo, Italia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>Questa struttura si trova a 6 minuti a piedi dalla spiaggia. Situato a Cupra Marittima, a 5 km da Grottammare, il Camping Terrazzo sul mare offre una piscina stagionale all'aperto e il WiFi gratuito.
-Tutte climatizzate, le sistemazioni includono una TV, una cucina interamente attrezzata con zona pranzo e un bagno privato con doccia.
-Il campeggio vanta una terrazza solarium e un salone in comune.
-Il Camping Terrazzo sul mare dista 10 km da San Benedetto del Tronto e 47 km da Porto Recanati. L’Aeroporto più vicino è quello di Ancona-Falconara, a 85 km.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | VISTA: Vista giardino, Vista mare, | SPAZI ALL'APERTO: Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, | CUCINA: Piano cottura, Utensili da cucina, Cucina, Frigorifero, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ATTIVITÀ: Spiaggia, Spiaggia privata
-a pagamento, Ping-pong, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI DI RISTORAZIONE: Bar, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Sala comune/zona TV, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | SERVIZI GENERALI: Aria condizionata, Ingresso indipendente, Disponibilità di camere familiari, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-terrazzo-sul-mare.it.html</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>camping-terrazzo-sul-mare</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EUROPING VILLAGE MARSIA Abruzzo</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>loc. homo selvatico, 67060 Marsia, Italia</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Situato a Marsia, in Abruzzo, l'EUROPING VILLAGE MARSIA Abruzzo offre un parcheggio privato gratuito.
-Al mattino vi attende una colazione all'italiana.
-Potrete inoltre rilassarvi nel giardino.
-Il campeggio dista 34 km da Tivoli e 30 km da Fiuggi. 57 km dall'Aeroporto di Roma-Ciampino, lo scalo più vicino.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Tutti gli alloggi per la vostra vacanza 
-Marsia vi aspetta con diversi tipi di alloggio, pronti a soddisfare ogni necessità e desiderio. Una struttura dove far star bene e divertire tutta la famiglia, un camping ideale per gli amanti della bici o per chi vuole godersi un weekend all’insegna del relax... Selezionate la categoria di vacanza che fa per voi e prenotate online in tutta sicurezza.
-l’area campeggio nel villaggio di montagna è dotata di ben 42 ampie piazzole di sosta, erbose e ben distanziate tra loro. Si trovano in un posizione privilegiata, su un terreno terrazzato, ai piedi della montagna e soleggiate e allo stesso tempo vicinissime a tutti i servizi e spazi comuni del villaggio
-Tra i numerosi servizi utili, la struttura offre ristorante con piatti d'asporto, market, servizi igienici , locale ritrovo, e wi-fi.
-Anche i cani sono ammessi, con un piccola quota aggiuntiva.
-Ritrova l'atmosfera di casa tua immergendoti nella natura dei boschi delle splendida Marsia trascorri la tua vacanza nei nuovi Chalet del Camping : nella classica struttura della baita di montagna,</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SPAZI ALL'APERTO: Area picnic, Barbecue, Giardino, | ANIMALI: | ATTIVITÀ: Happy hour
-a pagamento, Massaggi corpo, Massaggi mani, Massaggi testa, Massaggi piedi, Massaggi collo, Massaggi schiena, Escursionismo, Biliardo
-a pagamento, Massaggi, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
-a pagamento, Buffet per bambini, Pasti per bambini
-a pagamento, Menù per diete particolari (su richiesta), Snack bar, Possibilità di colazione in camera, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Deposito bagagli, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Giochi da tavolo/puzzle, | SERVIZI DI PULIZIA: Servizio pulizie giornaliero
-a pagamento, | SERVIZI BUSINESS: Fax/fotocopiatrice, Spazi per riunioni/banchetti
-a pagamento, | PROTEZIONE E SICUREZZA: Estintori, Allarme di sicurezza, Accesso con chiavi, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Consegna spesa a domicilio, Minimarket sul posto, Area fumatori, Riscaldamento, Possibilità di pranzo al sacco, Disponibilità di camere familiari, Camere non fumatori, Servizio in camera, | LINGUE PARLATE: Inglese, Italiano, Polacco, | </t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/europing-village-marsia-neve.it.html</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>europing-village-marsia-neve</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Parco Gessilandia</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Via Gesso 40 Localita Gesso 40, 61013 Sassofeltrio, Italia</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Situato a Sassofeltrio, il Parco Gessilandia offre una piscina all’aperto stagionale, un bar e un giardino.
-Gli alloggi comprendono un angolo cottura completamente accessoriato con frigorifero e fornelli. Alcune sistemazioni sono provviste di aria condizionata, TV e zona salotto e/o pranzo.
-Come ospiti potrete gustare una colazione a buffet.
-Il Parco Gessilandia dista 18 km da Rimini e 16 km da Riccione. L’Aeroporto Internazionale Federico Fellini, il più vicino, si trova a 16 km dalla struttura.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Bidet, Vasca o doccia, WC, Prodotti da bagno in omaggio, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Barbecue, Giardino, | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | SERVIZI DI RISTORAZIONE: Bar, | INTERNET: | PARCHEGGIO: Parcheggio in strada, | SERVIZI GENERALI: Aria condizionata, Disponibilità di camere familiari, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Giochi da piscina, Ombrelloni, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, | LINGUE PARLATE: Italiano, | </t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/parco-gessilandia.it.html</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>parco-gessilandia</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Camping Village Mar y Sierra</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Strada San Gervasio 3, 61039 San Costanzo, Italia</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>Situato a San Costanzo, il Camping Village Mar y Sierra vanta una piscina all'aperto, la connessione WiFi gratuita nelle aree comuni e camere climatizzate, in alcuni casi con terrazza.
 Ciascuna sistemazione presenta anche una TV a schermo piatto, una scrivania e un bagno privato con set di cortesia.
@@ -933,12 +828,12 @@
 Completo di parcheggio gratuito, il Camping Village Mar y Sierra dista, in auto, 10 minuti dalle spiagge della zona e 40 minuti da Pesaro.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>No camping host description</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Carta igienica, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Terrazza solarium, Barbecue, Terrazza, Giardino, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo, Spiaggia, Armadietti per fitness/spa, Attrezzatura da tennis, Parco acquatico
 Non sul posto
@@ -947,14 +842,184 @@
 a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Allarme antifumo, Allarme di sicurezza, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | PISCINA SCOPERTA: Stagionale, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-village-mar-y-sierra.it.html</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>camping-village-mar-y-sierra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Camping Villaggio Cortina</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lungomare Italia 1/1, 60019 Senigallia, Italia</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Il Camping Villaggio Cortina sorge sul lungomare di Senigallia, proprio di fronte alla spiaggia. Offre la connessione Wi-Fi gratuita nella zona della reception.
+Alcune unità sono dotate di aria condizionata, angolo cottura con frigorifero e zona pranzo.
+La struttura dispone di un bar in loco dove potrete gustare un drink. A vostra disposizione anche una spiaggia privata.
+Il Camping Cortina dista 5 km dalla stazione ferroviaria di Senigallia e 24 km da Ancona.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Da più di 15 anni ospitiamo famiglie, coppie e campeggiatori nella nostra struttura. 
+Abbiamo piazzole per tende, roulotte e camper e comode mobilhouse da 4 o 5 posti.
+Il nostro pacchetto all-inclusive vi permette di pagare una sola volta per avere tutto ciò che può servirvi, mobilhouse, parcheggio, pulizie animazione e servizio spiaggia tutto compreso!
+Voi dovrete portare soltando la crema solare!</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, | SPAZI ALL'APERTO: Arredamento da esterni, Barbecue, Terrazza, Giardino, | CUCINA: Frigorifero, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ATTIVITÀ: Spiaggia, Intrattenimento serale, Fronte spiaggia, Staff di animazione, Spiaggia privata, Windsurf
+Non sul posto
+a pagamento, Ping-pong, | SERVIZI DI RISTORAZIONE: Pasti per bambini
+a pagamento, Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | TRASPORTI: Biglietti per i mezzi di trasporto, | ALTRI SERVIZI: Servizio navetta, Servizio lavanderia
+a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Estintori, Accesso con chiavi, | SERVIZI GENERALI: Aria condizionata, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Lavabo più basso, WC con maniglioni, Accesso su sedia a rotelle, | SERVIZI BENESSERE: Ombrelloni, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/villaggio-cortina.it.html</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>villaggio-cortina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Poggio Imperiale Marche</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Contrada San Savino, 18, 62012 Civitanova Marche, Italia</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Situato a Civitanova Marche, il Poggio Imperiale Marche offre una piscina privata e una vista sul giardino. Ubicata a 50 km da Grosseto, questa struttura climatizzata presenta un parcheggio privato in loco e il WiFi gratuito.
+La casa vacanze dispone di 1 camera da letto, 1 bagno, asciugamani, lenzuola, TV a schermo piatto con canali satellitari, zona pranzo, cucina completamente attrezzata e patio con vista sulla piscina.
+In loco è presente un’area giochi per bambini. Potrete praticare escursioni a piedi o in bicicletta nella zona, godervi la piscina all’aperto o rilassarvi nel giardino e utilizzare le attrezzature per barbecue in loco.
+Il Poggio Imperiale Marche dista 22 km da Sirolo e 12 km da Porto Recanati. L’Aeroporto di Ancona-Falconara, lo scalo più vicino, è ubicato a 60 km.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: Parcheggio per disabili, Parcheggio custodito, | INTERNET: | CUCINA: Tavolo da pranzo, Piano cottura, Forno, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, Letti lunghi (oltre 2 metri), | BAGNO: Carta igienica, Asciugamani, Bidet, Bagno privato, WC, Asciugacapelli, Doccia, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali satellitari, TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Pavimento in marmo o in piastrelle, Ingresso indipendente, Vasca idromassaggio, | ANIMALI: | ACCESSIBILITÀ: Intera unità accessibile ai disabili, Intera unità situata al piano terra, | SPAZI ALL'APERTO: Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Piscina privata a uso esclusivo, Barbecue, Patio, Giardino, | PISCINA SCOPERTA: Aperta tutto l'anno, Accessibile a ogni età, Recinto attorno alla piscina, Sdraio/lettini, Ombrelloni, Piscina riscaldata, Piscina con vista, Piscina di acqua salata, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Vasca all'aperto, Hammam, Vasca idromassaggio/jacuzzi, Massaggi, Spa &amp; centro benessere
+a pagamento, Sauna
+a pagamento, | ATTIVITÀ: Mostre d'arte temporanee
+Non sul posto
+a pagamento, Equitazione
+a pagamento, Escursioni in bicicletta
+Non sul posto, Escursionismo
+Non sul posto, | ESTERNI E VISTA: Vista cortile interno, Vista piscina, Vista giardino, Vista mare, | CARATTERISTICHE DELL'EDIFICIO: Appartamento privato in edificio, Indipendente, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi, | SERVIZI DI PULIZIA: Servizio lavanderia, | VARIE: Lavabo più basso, WC con seduta più alta, WC con maniglioni, Accesso su sedia a rotelle, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, | LINGUE PARLATE: Arabo, Inglese, Spagnolo, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/poggio-imperiale-marche-civitanova-marche-5.it.html</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>poggio-imperiale-marche-civitanova-marche-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AGRITURISMO CASALE CIVETTA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20 Via Consolazione, 60010 Castel Colonna, Italia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Situated in Castel Colonna in the Marche region, AGRITURISMO CASALE CIVETTA features accommodation with free private parking.
+Some units are air conditioned and include a seating area with a CD player.
+Guests at the aparthotel can enjoy a continental or a buffet breakfast.
+AGRITURISMO CASALE CIVETTA offers a children's playground.
+Guests can swim in the outdoor swimming pool, go hiking or cycling, or relax in the garden and use the barbecue facilities.
+Sirolo is 43 km from the accommodation, while Ancona is 32 km from the property. The nearest airport is Ancona Falconara, 20 km from AGRITURISMO CASALE CIVETTA, and the property offers a paid airport shuttle service.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Casale Civetta, è in aperta campagna tra il Mare Adriatico di Senigallia e la città medievale di Corinaldo, in quella porzione di Marche dove la provincia di Ancona tocca quella di Pesaro e Urbino, è molto più di una meta dove trascorrere qualche giorno di vacanza.
+Un luogo di incontro ed espressione, un’oasi accogliente dove la creatività è la benvenuta e dove chiunque può liberare l’immaginazione.
+"Si può esistere senza arte, ma senza di essa non si può vivere" diceva Oscar Wilde, e non è certo un caso che la frase del brillante scrittore inglese sia diventata il motto dell’attività, visto che si sposa perfettamente con la filosofia che si può trovare a Casale Civetta.
+La natura è  una grande protagonista di questo luogo, perché il panorama sulle campagne marchigiane è davvero incantevole e lasciarsi rapire dalla cornice verde delle colline è sicuramente un bel modo per trovare relax. Ampi spazi aperti, pavimentati con mattoni.
+Una piscina panoramica sulle colline e le chiome degli alberi.
+Un laboratorio di scultura del tufo. Yoga. Bici Mbk.
+Una libreria ricavata dalla ex serra, luminosa e piena di libri d'arte, di storia e sulle Marche.
+Alberi da frutto</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bidet, Vasca o doccia, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Terrazza, Giardino, | CUCINA: Prodotti per le pulizie, Lavatrice, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Letto pieghevole, Zanzariera, Ingresso indipendente, Ferro e asse da stiro, Ferro da stiro, | ESTERNI E VISTA: Vista giardino, | ANIMALI: | ATTIVITÀ: Tiro con l'arco, Tour o lezioni sulla cultura locale, Tour in bicicletta, Tour a piedi, Mostre d'arte temporanee
+Non sul posto, Equitazione
+Non sul posto
+a pagamento, Escursioni in bicicletta
+Non sul posto, Escursionismo
+Non sul posto, | AREA SOGGIORNO: Scrivania, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
+a pagamento, Possibilità di pranzo al sacco, Bar, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, | TRASPORTI: Navetta per l'aeroporto
+a pagamento, Navetta dall'aeroporto
+a pagamento, Navetta aeroportuale (a pagamento), Servizio navetta (a pagamento), | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Armadietti, Check-in e check-out privati, Deposito bagagli, Check-in e check-out express, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Libri, DVD o musica per bambini, Area giochi, | SERVIZI DI PULIZIA: Servizio lavanderia
+a pagamento, | SERVIZI BUSINESS: Fax/fotocopiatrice, Spazi per riunioni/banchetti
+a pagamento, | PROTEZIONE E SICUREZZA: Accesso con chiavi, Sicurezza 24 ore su 24, | CARATTERISTICHE DELL'EDIFICIO: Appartamento privato in edificio, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Sdraio/lettini, Bar a bordo piscina, Piscina con vista, Piscina all'ultimo piano, Zona acqua bassa, | SERVIZI BENESSERE: Personal trainer, Lezioni di yoga, Massaggi corpo
+a pagamento, Massaggi mani
+a pagamento, Massaggi testa
+a pagamento, Massaggi di coppia
+a pagamento, Massaggi piedi
+a pagamento, Massaggi collo
+a pagamento, Massaggi schiena
+a pagamento, Sdraio/lettini, Massaggi
+a pagamento, | VARIE: Ciotole per animali domestici, Accesso su sedia a rotelle, Area fumatori, Riscaldamento, Disponibilità di camere insonorizzate, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | LINGUE PARLATE: Inglese, Spagnolo, Italiano, | </t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-village-mar-y-sierra.it.html</t>
+          <t>https://www.booking.com/hotel/it/agriturismo-casale-civetta.it.html</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>camping-village-mar-y-sierra</t>
+          <t>agriturismo-casale-civetta</t>
         </is>
       </c>
     </row>
@@ -964,45 +1029,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lodge Holidays - Camping Podere Sei Poorte</t>
+          <t>Conero Azzurro</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Via Petricci, 61020 Genga, Italia</t>
+          <t>Via Castelfidardo 80, 60026 Numana, Italia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lodge Holidays - Camping. Situato a Genga, il Podere Sei Poorte offre un ristorante, una piscina all'aperto e un bar. 38 km da Cattolica.
-L'alloggio presenta un'area salotto e un angolo cottura con frigorifero e fornelli.
-In loco troverete anche un'area giochi per bambini. Potrete rilassarvi nel giardino o nell'area salotto in comune.
-Il Camping Podere Sei Poorte dista 45 km da Riccione e 23 km da Pesaro. La struttura dista 30 km dall'Aeroporto Internazionale Federico Fellini, lo scalo più vicino.</t>
+          <t>Situato a Numana, nel Parco Regionale del Monte Conero, a 80 metri dalla spiaggia, il Conero Azzurro offre un ristorante, una piscina all'aperto e la connessione WiFi gratuita in tutte le aree comuni.
+Tutti i bungalow sono dotati di patio, angolo cottura, area salotto e bagno privato con doccia.
+Presso la vicina spiaggia privata potrete usufruire di un ombrellone e 2 lettini. La struttura fornisce inoltre personale di animazione e il parcheggio gratuito.
+Il villaggio turistico Conero Azzurro dista 10 minuti d'auto da Porto Recanati e 30 km da Ancona.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>If enjoying your holiday might mean more to you than just laying in the sun and could be a combination of just relaxing, cultural development, natural challenges and Italian gastronimical hospitality…………… than Campsite Podere Sei Poorte is your ideal destination. 
-This is truly a fabulous place to spend a holiday and enjoy all the beautiful things life has to offer. The restaurant conjures up delicious pure Italian dishes, à la carte, as well as themed evenings with a pizza buffet, fresh fish, or pasta e basta. 
-Sunday brunch is highly recommended. How wonderful to have a slow, culinary start to the day. A delicious buffet with fresh bread, salads, bruschetta, frittata and various Italian fillings. With a good cappuccino and juice, or a cheeky bianco frizzante!  - -In short, you need do nothing more here than unwind and enjoy yourself. 
-Laze in the perfectly appointed Fatboy hammock with panoramic views from your luxury Lodge Holidays lodge.</t>
+          <t>No camping host description</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: Stazione di ricarica per veicoli elettrici, Parcheggio custodito, | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | AREA SOGGIORNO: Zona soggiorno, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ACCESSIBILITÀ: Intera unità situata al piano terra, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Aperta tutto l'anno, Sdraio/lettini, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Ingresso indipendente, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Vasca comune (daiyokujo), Intrattenimento serale, Mini club, Escursioni in bicicletta, Noleggio biciclette (a pagamento), Ping-pong, Area giochi, | ALTRI SERVIZI: Sala comune/zona TV, Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
+          <t xml:space="preserve">SPAZI ALL'APERTO: Arredamento da esterni, Terrazza, Giardino, | ATTIVITÀ: Spiaggia, Fitness, Attrezzatura da tennis
+a pagamento, Intrattenimento serale, Fronte spiaggia, Mini club, Staff di animazione, Spiaggia privata, Area giochi, Campo da golf (nel raggio di 3 km)
+a pagamento, Campo da tennis
+a pagamento, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Sala comune/zona TV, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Riscaldamento, Ingresso indipendente, | PISCINA SCOPERTA: Stagionale, | SERVIZI BENESSERE: | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-podere-sei-poorte.it.html</t>
+          <t>https://www.booking.com/hotel/it/conero-azzurro.it.html</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>camping-podere-sei-poorte</t>
+          <t>conero-azzurro</t>
         </is>
       </c>
     </row>
@@ -1012,44 +1075,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Safaritent Glamping Mar Y Sierrra</t>
+          <t>Camping Gabicce Monte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>via S. Gervasio, 61039 Casa Castellani, Italia</t>
+          <t>148 Via Panoramica, 61011 Gabicce Mare, Italia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Situato a Casa Castellani, il Safaritent Glamping Mar Y Sierrra offre un ristorante, una piscina stagionale all'aperto e un bar. La struttura dista 37 km da Urbino e dispone di un parcheggio privato gratuito.
-In loco troverete anche un'area giochi per bambini. Durante il vostro soggiorno al Safaritent Glamping Mar Y Sierrra potrete giocare a ping pong in loco o esplorare i dintorni in bicicletta.
-La struttura dista 41 km da Ancona e 27 km da Pesaro. Il Safaritent Glamping Mar Y Sierrra dista 25 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
+          <t>Situato a Gabicce Mare, a meno di 1 km dalla spiaggia di Gabicce Mare e a 2,3 km dalla spiaggia di Cattolica, il Camping Gabicce Monte offre sistemazioni con WiFi gratuito, aria condizionata e accesso a un giardino con barbecue. In loco è presente un parcheggio privato.
+Tutti gli alloggi dispongono di patio, cucina con frigorifero, zona pranzo, area salotto con TV e bagno privato con bidet.
+Il campeggio ospita una terrazza.
+L’Aeroporto Internazionale Federico Fellini, il più vicino, è ubicato a 18 km dal Camping Gabicce Monte.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>No camping host description</t>
+          <t>Overlooking the sea between the lush greenery of San Bartolo Natural Park and the deep blue of the Adriatic, the cosy Camping Gabicce Monte will amaze you with its breathtaking sunrises and sunsets.
+It's a hidden gem for those who look for a holiday in true contact with nature, with simplicity and relaxation, surrounded by beauty. 
+Located just outside the delightful village of Gabicce Monte, where to find panoramic restaurants, bars, food shops and a little supermarket, it's a perfect choice for hiking and cycling enthusiasts. 
+Just below the Campsite lays a wonderful wild rocky beach with crystal clear waters: you can reach it on foot taking a challenging trail in the woods next to the Camping Gabicce Monte, an experience not to miss when you're in the area! 
+If you prefer the traditional and well equipped golden sandy beaches of Cattolica and Gabicce Mare, you can take advantage of public transport. 
+GIULIETTA and ROMEO are the new cozy vacation homes, born in 2021. Both immersed in the green and with a gorgeous panorama overlooking the sea. The houses are 8.00 x 3.00 meters with a large veranda of 20 s.q. meters and can host 4 people.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: Parcheggio per disabili, | INTERNET: | CUCINA: Utensili da cucina, | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | SPAZI ALL'APERTO: Arredamento da esterni, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Bar a bordo piscina, Ombrelloni, Scivolo d'acqua, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, Scivolo d'acqua, | SERVIZI GENERALI: Minimarket sul posto, Struttura interamente non fumatori, Zanzariera, Parquet o pavimento in legno, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Vino/champagne
-a pagamento, Pasti per bambini, Bar, Ristorante, Bollitore tè/macchina caffè, | ATTIVITÀ: Tour in bicicletta, Tour a piedi, Snorkeling
-Non sul posto, Equitazione
-Non sul posto, Escursioni in bicicletta
-Non sul posto, Vasca idromassaggio/jacuzzi, Windsurf
-Non sul posto, Ping-pong, Area giochi, Campo da tennis, | ALTRI SERVIZI: Check-in e check-out privati, | VISTA: Vista montagna, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | LINGUE PARLATE: Tedesco, Inglese, Italiano, Olandese, | </t>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani, Bidet, Vasca o doccia, Bagno privato, WC, Doccia, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Patio, Terrazza, Giardino, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Zanzariera, Ingresso indipendente, Riscaldamento, Camere non fumatori, | ALTRI SERVIZI: Consegna spesa a domicilio
+a pagamento, Distributore automatico di snack, Distributore automatico di bevande, | VISTA: Vista mare, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/safaritent-glamping-mar-y-sierrra.it.html</t>
+          <t>https://www.booking.com/hotel/it/camping-gabicce-monte.it.html</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>safaritent-glamping-mar-y-sierrra</t>
+          <t>camping-gabicce-monte</t>
         </is>
       </c>
     </row>
@@ -1059,45 +1124,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Antica Dimora - GLAMPING FIORDALISO</t>
+          <t>Camping Village Costa Verde</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C.DA CALLARELLA, 62028 Sarnano, Italia</t>
+          <t>Contrada Asola, 62018 Porto Potenza Picena, Italia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Situata a Sarnano, nelle Marche, l'ANTICA DIMORA - CAMPEGGIO FIORDALISO offre gratuitamente il WiFi e un parcheggio privato.
-Potrete nuotare nella piscina all'aperto, sciare o andare in bicicletta, o rilassarvi nel giardino e utilizzare il barbecue.
-Il campeggio dista 48 km da Grottammare e 44 km da Porto San Giorgio. L'ANTICA DIMORA - CAMPEGGIO FIORDALISO dista 63 km dall'Aeroporto di Ancona Falconara, lo scalo più vicino.</t>
+          <t>Questa struttura si trova a 3 minuti a piedi dalla spiaggia. Situato a Porto Potenza Picena, a 200 metri dalle spiagge di sabbia, il Camping Village Costa Verde offre una piscina all'aperto, un ristorante e la connessione Wi-Fi gratuita nelle aree comuni.
+La struttura metterà a vostra disposizione una reception aperta 24 ore su 24, programmi di intrattenimento serali e per bambini, un'area TV in comune e alcuni servizi a pagamento, come il noleggio di biciclette o di sedie a sdraio per la spiaggia privata.
+Provvisti di zona pranzo all'aperto, angolo cottura completamente attrezzato, area salotto e bagno privato con doccia, gli alloggi in alcuni casi dispongono di un patio o balcone.
+Oltre alla ristorazione indipendente nelle sistemazioni, presso il Costa Verde Camping potrete usufruire di attrezzature comuni per il barbecue, di uno snack bar e di un ristorante.
+Dotato di parcheggio gratuito, il campeggio dista 11,5 km da Porto Sant'Elpidio e 20 minuti di auto dal punto di inizio del Parco Regionale del Conero.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Il campeggio Fiordaliso è stato pensato per offrire agli ospiti un ambiente naturale e verde, con una bella vista sui Monti Sibillini  godendo di tutti i nuovissimi servizi appena allestiti e di una bella piscina. E' un campeggio per tende e roulotte.
-Abbiamo voluto creare un ambiente per "volare al di fuori del tempo", nei luoghi magici e fantastici di " Alice nel Paese delle Meraviglie".
-Potrete alloggiare in delle bellissime roulotte rivisitate dove incontrerete lo Stregatto o il  Bianconiglio o piuttosto il Cappellaio Magico perchè la nostra parola d'ordine è MERAVIGLIARSI SEMPRE....meravigliarsi delle lucciole che ci fanno luce nelle sere di giugno , delle stelle così brillanti che sembra di toccare con la mano, dei concerti al chiaro di luna intonati dalle nostre rane, dalla tenerezza di tutti i nostri amici della fattoria che ci fanno da cornice. 
-C'è un posto che non ha eguali sulla terra....Questo luogo è un luogo unico al mondo, una terra colma di meraviglie, mistero e pericolo. Si dice che per sopravvivere qui bisogna essere matti come un cappellaio. E per fortuna...io lo sono. "</t>
+          <t>Il Camping Village Costa Verde si trova nelle Marche, a pochi chilometri da una delle aree più suggestive della splendida riviera Adriatica, il Parco naturale del Conero.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | BAGNO: Bagno in comune, | SPAZI ALL'APERTO: Area picnic, Barbecue, Giardino, | PISCINA SCOPERTA: Stagionale, Sdraio/lettini, Piscina con vista, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | SERVIZI GENERALI: Disponibilità di camere familiari, Camere non fumatori, | ATTIVITÀ: Tour in bicicletta
-a pagamento, Tour a piedi, Escursioni in bicicletta
-Non sul posto, Escursionismo
-Non sul posto, Noleggio biciclette (a pagamento), Sci, | ALTRI SERVIZI: Check-in e check-out express, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Accesso con chiavi, | LINGUE PARLATE: Inglese, Italiano, | </t>
+          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Intrattenimento serale, Attrezzature per sport acquatici sul posto
+a pagamento, Staff di animazione, Spiaggia privata
+a pagamento, Escursioni in bicicletta, Freccette, Windsurf
+a pagamento, Karaoke, Area giochi, Sala giochi, | AREA SOGGIORNO: Zona pranzo, | SERVIZI DI RISTORAZIONE: Bar, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio pulizie giornaliero
+a pagamento, Sala comune/zona TV, Fax/fotocopiatrice
+a pagamento, Banco escursioni, Servizio lavanderia
+a pagamento, Reception 24 ore su 24, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | SERVIZI GENERALI: Aria condizionata
+a pagamento, Riscaldamento, Disponibilità di camere familiari, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/antica-dimora-campeggio-fiordaliso.it.html</t>
+          <t>https://www.booking.com/hotel/it/camping-village-costa-verde.it.html</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>antica-dimora-campeggio-fiordaliso</t>
+          <t>camping-village-costa-verde</t>
         </is>
       </c>
     </row>
@@ -1107,332 +1175,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Resort Orizzonti Glamping</t>
+          <t>CIVETTUOLA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1081 Via Monte Taccone, 63811 Sant'Elpidio a Mare, Italia</t>
+          <t>20 Via Consolazione, 60010 Castel Colonna, Italia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>Set in SantʼElpidio a Mare, Resort Orizzonti Glamping offers accommodation with air conditioning and access to a garden with an outdoor swimming pool.
-There is a fully equipped private bathroom with shower and a hairdryer.
-The tented camp provides a barbecue.
-San Benedetto del Tronto is 36 km from Resort Orizzonti Glamping, while Sirolo is 31 km away. The nearest airport is Ancona Falconara Airport, 48 km from the accommodation.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>La collocazione sopraelevata garantisce un'incantevole vista sulle colline marchigiane e sugli spazi verdi della Riserva naturale, all'orizzonte  scorgono  i monti Sibillini,  dal  Vettore,alla Sibilla  .Questa vista garantisce riservatezza e tranquillità.Attorno un ampio giardino verde con incantevoli ulivi anche secolari, piscina con vista   e con i suoi 3 appartamenti con ingresso indipendenti 2 tende Glampin di lusso completi di ogni confort, .Rende così  il resort Orizzonti un posto unico e speciale.  Siamo noi tutto lo staff di Resort Orizzonti, a prenderci cura di ogni nostro ospite, che aver così accesso non soltanto a una location di pregio ma a un'esperienza esclusiva .</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | CUCINA: Cucina in comune, Tavolo da pranzo, Utensili da cucina, Frigorifero, | SERVIZI IN CAMERA: Stand appendiabiti, | ANIMALI: | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Possibilità di pranzo al sacco, Servizio lavanderia, | SERVIZI GENERALI: Area fumatori, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Italiano, | </t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/resort-orizzonti-glamping.it.html</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>resort-orizzonti-glamping</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Camping Blu Fantasy</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Lungomare Italia 3B, 60019 Senigallia, Italia</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Situato sul lungomare, a 4 km da Senigallia, il Camping Blu Fantasy offre appartamenti a ristorazione indipendente, una piscina all’aperto e un giardino con barbecue. Il WiFi è fruibile gratuitamente nelle aree comuni.
-Tutti gli appartamenti sono dotati di aria condizionata, TV a schermo piatto e angolo cottura con forno e frigorifero. Presentano anche un bagno privato con doccia e bidè.
-I più piccoli apprezzeranno il programma di intrattenimento e l’area giochi a loro dedicati. Tra i servizi troverete inoltre un bar, un minimarket e un ristorante esterno convenzionato con trattamento di mezza pensione e pensione completa.
-Il Camping Villaggio Blu si trova a 15 minuti d’auto da Falconara Marittima e a 30 km da Jesi.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>La data di apertura del Villaggio è prevista dal 1° giugno all'11 settembre 2022 compreso, con tutti i servizi operativi, nel rispetto delle norme governative sulla sicurezza e la salute dei nostri ospiti. 
-La biancheria NON è inclusa nel prezzo del soggiorno. Il kit di biancheria completo da letto e da bagno è valido per l'intero soggiorno ed è da noleggiare su richiesta al momento della prenotazione del soggiorno. Il costo per un kit matrimoniale è di 18 Euro, mentre quello del kit singolo di 11,5 Euro. In alternativa si dovrà utilizzare la propria biancheria dal letto e da bagno.
-Il servizio spiaggia NON è incluso nel prezzo del soggiorno. Vi sono 2 stabilimenti balneari con sabbia aggiunta nelle vicinanze; spiaggia convenzionata "TRILLO 148" a 600 metri oppure spiaggia NON convenzionata "Bahya Blanca"a 150 metri (più piccola e meno attrezzata). Spiaggia libera di ghiaia con fondale sabbioso di fronte a noi, a 50 metri.
-Vi aspettiamo!</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Barbecue, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Aerobica, Cabaret, Intrattenimento serale, Mini club, Staff di animazione, Vasca idromassaggio/jacuzzi, Freccette, Karaoke, Ping-pong, Area giochi, | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali satellitari, | SERVIZI DI RISTORAZIONE: Frutta
-a pagamento, Vino/champagne
-a pagamento, Buffet per bambini, Pasti per bambini, Menù per diete particolari (su richiesta), Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio in strada, | ALTRI SERVIZI: Servizio navetta, Sala comune/zona TV, Servizio navetta (gratuito), Possibilità di pranzo al sacco, Servizio lavanderia
-a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Cancelletti di sicurezza per bambini, Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Struttura interamente non fumatori, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | 2 PISCINE: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Zona acqua bassa, Anche per bambini, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Inglese, Francese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/villaggio-camping-blu.it.html</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>villaggio-camping-blu</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Tobacco Road camping Sirolo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Via Peschiera 9, 60020 Sirolo, Italia</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Questa struttura si trova a 18 minuti a piedi dalla spiaggia. Situato a Sirolo, il Tobacco Road camping Sirolo offre una vista sulla sua piscina, un bar, un salotto in comune e sistemazioni con WiFi gratuito.
-Le unità dispongono di patio, cucina con frigorifero, zona pranzo, area soggiorno con TV a schermo piatto e bagno privato con doccia.
-Presso il campeggio troverete un barbecue.
-I famosi luoghi di interesse nelle vicinanze del Tobacco Road camping Sirolo includono le spiagge di Urbani, San Michele e Numana. L’Aeroporto di Ancona-Falconara, il più vicino, sorge a 23 km.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Vasca o doccia, Bagno privato, WC, Doccia, | VISTA: Vista piscina, | SPAZI ALL'APERTO: Area picnic, Zona pranzo all'aperto, Barbecue, Patio, | CUCINA: Tavolo da pranzo, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Stand appendiabiti, | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo
-Non sul posto, Happy hour
-a pagamento, Windsurf
-Non sul posto
-a pagamento, Campo da golf (nel raggio di 3 km)
-a pagamento, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Pasti per bambini
-a pagamento, Snack bar, Bar, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, | TRASPORTI: Biglietti per i mezzi di trasporto
-a pagamento, | ALTRI SERVIZI: Sala comune/zona TV, Check-in e check-out privati, Possibilità di pranzo al sacco, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Telecamere a circuito chiuso all'esterno della struttura, Telecamere a circuito chiuso nelle zone in comune, Accesso con chiavi, Sicurezza 24 ore su 24, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Insonorizzazione, Ingresso indipendente, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Orari di apertura, Accessibile a ogni età, Recinto attorno alla piscina, Sdraio/lettini, Bar a bordo piscina, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/tobacco-road.it.html</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>tobacco-road</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Camping Liana</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lungomare Leonardo da Vinci 54 ter, 60019 Senigallia, Italia</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Situato a Senigallia, a 26 km da Ancona, il Camping Liana offre un ristorante e la connessione WiFi gratuita.
-La sistemazione dispone di aria condizionata, TV a schermo piatto, cucina interamente attrezzata con zona pranzo e bagno privato completo di doccia. Potrete usufruire di lenzuola e asciugamani a costo aggiuntivo.
-Presso il campeggio potrete gustare al mattino una colazione all’italiana.
-Il Camping Liana dista 35 km da Sirolo e 44 km da Porto Recanati. L’Aeroporto di Ancona-Falconara, lo scalo più vicino, sorge a 27 km.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista luogo di interesse, Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Spiaggia privata
-a pagamento, | AREA SOGGIORNO: Zona pranzo, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Zanzariera, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | LINGUE PARLATE: Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-liana.it.html</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>camping-liana</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Camping Norina</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Via Marina Ardizia 181, 61122 Pesaro, Italia</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Ubicato a Pesaro, il Camping Norina vanta un ristorante, un centro fitness e una spiaggia privata, e offre la connessione WiFi gratuita in tutte le aree.
-Tutti gli alloggi sono climatizzati e dotati di TV a schermo piatto e di bagno privato con asciugacapelli.
-Presso il Camping Norina avrete a disposizione delle attrezzature per sport acquatici, il miniclub e un'area giochi per bambini.
-La struttura dista 10 minuti di auto da Pesaro e da Fano e 23 km da Cattolica.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>No camping host description</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Attrezzature per sport acquatici sul posto, Spiaggia privata, Area giochi, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-norina.it.html</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>camping-norina</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Camping Pineta</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Via ca' mignone 5, 61029 Urbino, Italia</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Situato a Urbino, il Camping Pineta offre piscina, ristorante, bar, vista città e WiFi gratuito.
-Le sistemazioni comprendono patio, cucina con frigorifero, zona pranzo, salotto con TV e bagno privato con bidè e asciugacapelli. Per maggiore comodità, potrete usufruire di asciugamani e lenzuola ad un costo aggiuntivo.
-In loco avrete a disposizione una terrazza.
-Il Camping Pineta dista 5 km dal Duomo. L’Aeroporto Internazionale Federico Fellini è lo scalo più vicino, a 57 km dalla struttura.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ll Camping “Pineta” di Urbino è sorto in un'area di circa 22.000 metri quadri a est della citta, situato in una posizione eccellente sia dal punto di vista paesaggistico che da quello funzionale. Infatti si tratta di un terreno in declivio verso la città dal quale si gode un'ottima vista del Centro Storico. ll terreno dove sorge il Camping e in gran parte coperto da una folta pineta dando al campeggiatore uno stretto rapporto con Ia natura e il paesaggio circostante.  I servizi interni del Camping comprendono: bagni, lavandini, Iavelli, lavatoi, docce calde e fredde, fontane e torrette a norme CEE per prese di corrente (220 WT) dislocate in vari punti del terreno, tutto nelle proporzioni previste dalla legge; inoltre funzionano un Bar, un ristorante , piscina e sono disponibili anche bungalow .</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Asciugacapelli, Doccia, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Letto pieghevole, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Patio, Terrazza, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: | SERVIZI GENERALI: Soluzioni anallergiche, Aria condizionata, Zanzariera, Parquet o pavimento in legno, Riscaldamento, Insonorizzazione, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Bar, | ATTIVITÀ: Solarium, | VISTA: Vista luogo di interesse, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-pineta-urbino.it.html</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>camping-pineta-urbino</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Camping Paradiso</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Via Rive Del Faro 2, 61121 Pesaro, Italia</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Questa struttura si trova a 12 minuti a piedi dalla spiaggia. Ubicato nel parco regionale di San Bartolo, a 850 metri da Castel di Mezzo, il Camping Paradiso offre una piscina all'aperto e un barbecue.
-I bungalow e gli chalet dispongono di una terrazza con vista sulle montagne, di un'area salotto e, in alcuni casi, di un'angolo cottura e di una TV a schermo piatto.
-Al mattino, presso il bar in loco vi attende una prima colazione a base di cappuccino e croissant freschi. Troverete anche un ristorante, aperto nei mesi estivi, che propone la pizza.
-Il Camping Paradiso si trova a 12 km da Pesaro, e in auto dista 15 minuti dalla stazione di Cattolica e 25 minuti da Riccione.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>La nostra peculiarità è l'atmosfera familiare unita a servizi di qualità. Da sempre i nostri ospiti possono contare sul nostro aiuto per risolvere ogni problematica ed esigenza. Non è raro trovarsi la sera insieme al bar o ristorante a scambiarci battute come amici di vecchia data. Spesso i rapporti continuano anche dopo le vacanze e le famiglie tornano a trovarci per più anni.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Patio, Terrazza, Giardino, | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Cucina, Frigorifero, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, | ATTIVITÀ: Vasca all'aperto, Escursioni in bicicletta, Escursionismo, Freccette, Ping-pong, Area giochi, Pesca
-a pagamento, Campo da golf (nel raggio di 3 km)
-a pagamento, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Sala comune/zona TV, Deposito bagagli, Fax/fotocopiatrice, Possibilità di pranzo al sacco, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Giochi da tavolo/puzzle, | PROTEZIONE E SICUREZZA: Telecamere a circuito chiuso nelle zone in comune, Cassaforte, | SERVIZI GENERALI: Minimarket sul posto, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Sdraio/lettini, Piscina con vista, Piscina di acqua salata, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Tedesco, Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-paradiso.it.html</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>camping-paradiso</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CIVETTUOLA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>20 Via Consolazione, 60010 Castel Colonna, Italia</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
         <is>
           <t>CIVETTUOLA is situated in Castel Colonna and offers a bar and a terrace. The property is 8 km from Senigallia and free private parking is available.
 Towels and bed linen are provided.
@@ -1441,12 +1192,12 @@
 Sirolo is 43 km from CIVETTUOLA, while Ancona is 32 km from the property. The nearest airport is Ancona Falconara Airport, 20 km from the accommodation.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Piccola tenda fissa posizionata nel bordo del parco della struttura principale. Intima, esclusiva, panoramica.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Prodotti per le pulizie, Utensili da cucina, Lavatrice, Frigorifero, | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Servizi igienici in comune, Bagno privato, Doccia, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, | ANIMALI: | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Patio, Balcone, Terrazza, Giardino, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Giochi da piscina, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: Sdraio/lettini, | SERVIZI GENERALI: Ciotole per animali domestici, Ceste per animali domestici, Area fumatori, Ingresso indipendente, Possibilità di pranzo al sacco, Navetta aeroportuale, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Frutta
 a pagamento, Vino/champagne
@@ -1470,129 +1221,256 @@
 a pagamento, | PROTEZIONE E SICUREZZA: Accesso con chiavi, Sicurezza 24 ore su 24, | LINGUE PARLATE: Inglese, Spagnolo, Italiano, | </t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.booking.com/hotel/it/civettuola.it.html</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>civettuola</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Camping Village Costa Verde</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Contrada Asola, 62018 Porto Potenza Picena, Italia</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Questa struttura si trova a 3 minuti a piedi dalla spiaggia. Situato a Porto Potenza Picena, a 200 metri dalle spiagge di sabbia, il Camping Village Costa Verde offre una piscina all'aperto, un ristorante e la connessione Wi-Fi gratuita nelle aree comuni.
-La struttura metterà a vostra disposizione una reception aperta 24 ore su 24, programmi di intrattenimento serali e per bambini, un'area TV in comune e alcuni servizi a pagamento, come il noleggio di biciclette o di sedie a sdraio per la spiaggia privata.
-Provvisti di zona pranzo all'aperto, angolo cottura completamente attrezzato, area salotto e bagno privato con doccia, gli alloggi in alcuni casi dispongono di un patio o balcone.
-Oltre alla ristorazione indipendente nelle sistemazioni, presso il Costa Verde Camping potrete usufruire di attrezzature comuni per il barbecue, di uno snack bar e di un ristorante.
-Dotato di parcheggio gratuito, il campeggio dista 11,5 km da Porto Sant'Elpidio e 20 minuti di auto dal punto di inizio del Parco Regionale del Conero.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Il Camping Village Costa Verde si trova nelle Marche, a pochi chilometri da una delle aree più suggestive della splendida riviera Adriatica, il Parco naturale del Conero.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Intrattenimento serale, Attrezzature per sport acquatici sul posto
-a pagamento, Staff di animazione, Spiaggia privata
-a pagamento, Escursioni in bicicletta, Freccette, Windsurf
-a pagamento, Karaoke, Area giochi, Sala giochi, | AREA SOGGIORNO: Zona pranzo, | SERVIZI DI RISTORAZIONE: Bar, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio pulizie giornaliero
-a pagamento, Sala comune/zona TV, Fax/fotocopiatrice
-a pagamento, Banco escursioni, Servizio lavanderia
-a pagamento, Reception 24 ore su 24, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | SERVIZI GENERALI: Aria condizionata
-a pagamento, Riscaldamento, Disponibilità di camere familiari, | LINGUE PARLATE: Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/camping-village-costa-verde.it.html</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>camping-village-costa-verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>agriturismo la viola e il sole</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Contrada Vallasciano,41, 63900 Fermo, Italia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Situato a Fermo, l'agriturismo la viola e il sole offre una piscina stagionale all'aperto, un giardino, un barbecue. L'alloggio si trova a 28 km da Porto Recanati, e gli ospiti beneficiano di WiFi gratuito e un parcheggio privato in loco.
+Questo campeggio con tende presenta un'area salotto, una cucina con forno a microonde e una TV a schermo piatto.
+Presso il campo di tende avrete a disposizione una terrazza.
+L'agriturismo la viola e il sole dista 38 km da San Benedetto del Tronto e da Sirolo. L'Aeroporto più vicino è quello di Ancona-Falconara, a 55 km.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Le nostre due tende luxury sono affacciate sulle dolci colline marchigiane e baciate dal sole, ideali per il glamping, hanno una superficie di 54m2.
+Sono dotate di camera matrimoniale con letto a baldacchino, camera con 3 letti di cui uno a castello; dispongono di bagno privato con cabina doccia, cucina completamente accessoriata di stoviglie con tavolo e sedie ed ampia veranda.
+L’ambiente è caldo ed accogliente;i due teli frontali aperti consentono alla zona giorno di creare uno spazioso open-space con la veranda.
+Durante il soggiorno vi verranno fornite inoltre lenzuola, asciugamani,aria condizionata,TV e WIFI.
+Gli ospiti possono inoltre usufruire della piscina situata proprio in prossimità delle tende.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Prodotti per le pulizie, Piano cottura, Asciugatrice, Utensili da cucina, Bollitore elettrico, Cucina, Forno a microonde, Frigorifero, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, Cabina armadio, | BAGNO: Carta igienica, Asciugamani, Vasca o doccia, Bagno privato, WC, Prodotti da bagno in omaggio, Asciugacapelli, Doccia, | AREA SOGGIORNO: Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ACCESSIBILITÀ: Intera unità situata al piano terra, | SPAZI ALL'APERTO: Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Barbecue, Barbecue, Terrazza, Giardino, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Teli da piscina/spiaggia, Sdraio/lettini, Piscina con vista, | SERVIZI BENESSERE: Sdraio/lettini, Teli da piscina/spiaggia, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Zanzariera, Parquet o pavimento in legno, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Vino/champagne
+a pagamento, Possibilità di colazione in camera, Bollitore tè/macchina caffè, | ALTRI SERVIZI: Servizio lavanderia, | VISTA: Vista luogo di interesse, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, | PROTEZIONE E SICUREZZA: Estintori, Allarme antifumo, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/agriturismo-la-viola-e-il-sole.it.html</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>agriturismo-la-viola-e-il-sole</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Resort Orizzonti Glamping</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1081 Via Monte Taccone, 63811 Sant'Elpidio a Mare, Italia</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Set in SantʼElpidio a Mare, Resort Orizzonti Glamping offers accommodation with air conditioning and access to a garden with an outdoor swimming pool.
+There is a fully equipped private bathroom with shower and a hairdryer.
+The tented camp provides a barbecue.
+San Benedetto del Tronto is 36 km from Resort Orizzonti Glamping, while Sirolo is 31 km away. The nearest airport is Ancona Falconara Airport, 48 km from the accommodation.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>La collocazione sopraelevata garantisce un'incantevole vista sulle colline marchigiane e sugli spazi verdi della Riserva naturale, all'orizzonte  scorgono  i monti Sibillini,  dal  Vettore,alla Sibilla  .Questa vista garantisce riservatezza e tranquillità.Attorno un ampio giardino verde con incantevoli ulivi anche secolari, piscina con vista   e con i suoi 3 appartamenti con ingresso indipendenti 2 tende Glampin di lusso completi di ogni confort, .Rende così  il resort Orizzonti un posto unico e speciale.  Siamo noi tutto lo staff di Resort Orizzonti, a prenderci cura di ogni nostro ospite, che aver così accesso non soltanto a una location di pregio ma a un'esperienza esclusiva .</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | CUCINA: Cucina in comune, Tavolo da pranzo, Utensili da cucina, Frigorifero, | SERVIZI IN CAMERA: Stand appendiabiti, | ANIMALI: | AREA SOGGIORNO: Zona pranzo, Zona soggiorno, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Possibilità di pranzo al sacco, Servizio lavanderia, | SERVIZI GENERALI: Area fumatori, Aria condizionata, Struttura interamente non fumatori, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: Ombrelloni, Sdraio/lettini, | LINGUE PARLATE: Italiano, | </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/resort-orizzonti-glamping.it.html</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>resort-orizzonti-glamping</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Glamping Marche Nascoste Tenda e intero alloggio</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>41 Strada Provinciale 54, 62020 Penna San Giovanni, Italia</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Located in Penna San Giovanni in the Marche region, Glamping Marche Nascoste Tenda e intero alloggio features a garden. The property is 39 km from Grottammare and free private parking is provided.
-The tented camp also provides a fully equipped kitchen with a fridge, a seating area, a washing machine and 1 bathroom with a bidet and a bath.
+There is a seating area, a dining area and a kitchen complete with a fridge, an oven and a stovetop.
 An Italian breakfast is available daily at the tented camp.
-San Benedetto del Tronto is 41 km from Glamping Marche Nascoste Tenda, while Porto Recanati is 47 km away. The nearest airport is Ancona Falconara Airport, 61 km from the accommodation.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+San Benedetto del Tronto is 41 km from Glamping Marche Nascoste Tenda e intero alloggio, while Porto Recanati is 47 km away. The nearest airport is Ancona Falconara Airport, 61 km from the accommodation.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Nel piccolo borgo di Penna San Giovanni potrete soggiornare nella tenda Sibilla ,all'ombra degli alberi del nostro giardino con vista sui Sibillini, tra ulivi e fiori. Tenda di 5 m di diametro arredata (max 4 pers.) e intero alloggio privato con bagno, cucina, una camera (altre 2 pers.), sala e intrattenimento per vivere momenti meravigliosi. L'alloggio può ospitare fino a 6 persone dello stesso nucleo.
 Colazione con prodotti freschi locali. Noleggio bici, trekking, spiagge nelle vicinanze e molto altro!
 La nostra filosofia: green, fai da te, riutilizzo per limitare l'impatto ambientale.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Tavolo da pranzo, Prodotti per le pulizie, Tostapane, Piano cottura, Forno, Utensili da cucina, Cucina, Lavatrice, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Asciugamani, Bidet, Vasca o doccia, Servizi igienici in comune, Bagno privato, WC, Prodotti da bagno in omaggio, Asciugacapelli, Vasca, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue, Giardino, | SERVIZI GENERALI: Zanzariera, Pavimento in marmo o in piastrelle, Ingresso indipendente, Riscaldamento, Ventilatore, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Frutta, Vino/champagne
 a pagamento, Possibilità di colazione in camera, Bollitore tè/macchina caffè, | ATTIVITÀ: Freccette, Ping-pong, | ALTRI SERVIZI: Ciotole per animali domestici, Servizio lavanderia, | VISTA: Vista montagna, Vista giardino, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, Giochi da tavolo/puzzle, | LINGUE PARLATE: Tedesco, Inglese, Spagnolo, Italiano, | </t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.booking.com/hotel/it/glamping-marche-nascoste-tenda-e-intero-alloggio.it.html</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>glamping-marche-nascoste-tenda-e-intero-alloggio</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Camping Pineta</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Via ca' mignone 5, 61029 Urbino, Italia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Situato a Urbino, il Camping Pineta offre piscina, ristorante, bar, vista città e WiFi gratuito.
+Le sistemazioni comprendono patio, cucina con frigorifero, zona pranzo, salotto con TV e bagno privato con bidè e asciugacapelli. Per maggiore comodità, potrete usufruire di asciugamani e lenzuola ad un costo aggiuntivo.
+In loco avrete a disposizione una terrazza.
+Il Camping Pineta dista 5 km dal Duomo. L’Aeroporto Internazionale Federico Fellini è lo scalo più vicino, a 57 km dalla struttura.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ll Camping “Pineta” di Urbino è sorto in un'area di circa 22.000 metri quadri a est della citta, situato in una posizione eccellente sia dal punto di vista paesaggistico che da quello funzionale. Infatti si tratta di un terreno in declivio verso la città dal quale si gode un'ottima vista del Centro Storico. ll terreno dove sorge il Camping e in gran parte coperto da una folta pineta dando al campeggiatore uno stretto rapporto con Ia natura e il paesaggio circostante.  I servizi interni del Camping comprendono: bagni, lavandini, Iavelli, lavatoi, docce calde e fredde, fontane e torrette a norme CEE per prese di corrente (220 WT) dislocate in vari punti del terreno, tutto nelle proporzioni previste dalla legge; inoltre funzionano un Bar, un ristorante , piscina e sono disponibili anche bungalow .</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: | INTERNET: | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | BAGNO: Carta igienica, Asciugamani, Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Asciugacapelli, Doccia, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Divano letto, Stendibiancheria, Letto pieghevole, Stand appendiabiti, | ANIMALI: | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Terrazza solarium, Patio, Terrazza, | PISCINA SCOPERTA: Stagionale, Recinto attorno alla piscina, Piscina con vista, Zona acqua bassa, | SERVIZI BENESSERE: | SERVIZI GENERALI: Soluzioni anallergiche, Aria condizionata, Zanzariera, Parquet o pavimento in legno, Riscaldamento, Insonorizzazione, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | SERVIZI DI RISTORAZIONE: Bar, | ATTIVITÀ: Solarium, | VISTA: Vista luogo di interesse, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-pineta-urbino.it.html</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>camping-pineta-urbino</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camping Liana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lungomare Leonardo da Vinci 54 ter, 60019 Senigallia, Italia</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Situato a Senigallia, a 26 km da Ancona, il Camping Liana offre un ristorante e la connessione WiFi gratuita.
+La sistemazione dispone di aria condizionata, TV a schermo piatto, cucina interamente attrezzata con zona pranzo e bagno privato completo di doccia. Potrete usufruire di lenzuola e asciugamani a costo aggiuntivo.
+Presso il campeggio potrete gustare al mattino una colazione all’italiana.
+Il Camping Liana dista 35 km da Sirolo e 44 km da Porto Recanati. L’Aeroporto di Ancona-Falconara, lo scalo più vicino, sorge a 27 km.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Carta igienica, Asciugamani, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Biancheria per la casa, Armadio o guardaroba, | VISTA: Vista luogo di interesse, Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Seggiolone, Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Spiaggia privata
+a pagamento, | AREA SOGGIORNO: Zona pranzo, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Giochi da tavolo/puzzle, | SERVIZI GENERALI: Aria condizionata, Struttura interamente non fumatori, Zanzariera, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-liana.it.html</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>camping-liana</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Camping Spiaggia di Velluto</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Lungomare Leonardo da Vinci, 60019 Senigallia, Italia</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Situato a Senigallia, nelle Marche, il Camping Spiaggia di Velluto offre sistemazioni con parcheggio privato gratuito.
 Tutti gli alloggi comprendono divano, salotto, TV via cavo a schermo piatto, angolo cottura ben attrezzato e bagno privato con bidè e doccia. Per maggiore comodità, potrete usufruire di asciugamani e lenzuola a un costo aggiuntivo.
@@ -1601,7 +1479,7 @@
 La struttura si trova a 34 km da Sirolo e a 43 km da Porto Recanati. L'Aeroporto di Ancona-Falconara è lo scalo più vicino, a 12 km dal Camping Spiaggia di Velluto.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Dal diradare delle splendide colline marchigiane al mare si trova il camping Spiaggia di Velluto di Senigallia, polo turistico delle Marche, che accoglie da sempre visitatori da ogni parte del mondo.
 Il nostro campeggio, con una superficie di 15.000 mq., si affacciata direttamente sulle spiagge basse e sabbiose del litorale adriatico ed è il luogo ideale per famiglie e bambini in cui trascorrere le vostre vacanze in relax.
@@ -1609,70 +1487,222 @@
 Il servizio di pensione completa o mezza pensione è disponibile presso un ristorante convenzionato situato vicino alla nostra struttura.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">BAGNO: Bidet, Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Terrazza, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, | ATTIVITÀ: Spiaggia, Fronte spiaggia, Spiaggia privata, Windsurf, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, Scrivania, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali via cavo, TV, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio navetta, Servizio navetta (gratuito), Servizio lavanderia
 a pagamento, | PROTEZIONE E SICUREZZA: Estintori, | SERVIZI GENERALI: Aria condizionata, Zanzariera, Ingresso indipendente, Riscaldamento, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Intera unità situata al piano terra, | SERVIZI BENESSERE: Sdraio/lettini, | LINGUE PARLATE: Inglese, Italiano, | </t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/camping-spiaggia-di-velluto.it.html</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>camping-spiaggia-di-velluto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ai due Camini</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>via Rossini, 2 A, 62011 Cingoli, Italia</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Situato nella località marchigiana di Cingoli, l'Ai due Camini offre un giardino. 35 km da Ancona.
+Dotato di un balcone, questo campeggio climatizzato dispone di una cucina completamente attrezzata e di una TV. Le lenzuola e gli asciugamani sono inclusi.
+Come ospiti del campeggio potrete usufruire di una terrazza.
+La struttura Ai due Camini dista 36 km da Sirolo e 37 km da Porto Recanati. L'Aeroporto più vicino è quello di Ancona-Falconara, a 26 km.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARCHEGGIO: Parcheggio custodito, | INTERNET: | CUCINA: Piano cottura, Forno, Cucina, Frigorifero, Angolo cottura, | CAMERA DA LETTO: Biancheria per la casa, | BAGNO: Carta igienica, Asciugamani, Bidet, Vasca o doccia, Bagno privato, Accappatoio, Vasca, Doccia, | MEDIA E TECNOLOGIA: TV, | SERVIZI IN CAMERA: Stand appendiabiti, | ANIMALI: | ACCESSIBILITÀ: Intera unità accessibile ai disabili, Intera unità situata al piano terra, | SPAZI ALL'APERTO: Arredamento da esterni, Balcone, Terrazza, Giardino, | SERVIZI GENERALI: Aria condizionata, Ingresso indipendente, Disponibilità di camere comunicanti, Riscaldamento, Disponibilità di camere familiari, Camere non fumatori, | VISTA: Vista giardino, | LINGUE PARLATE: Italiano, | </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/ai-due-camini.it.html</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ai-due-camini</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Amapolas - Villaggio &amp; Camping</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Via Villagrande 125, 61024 Mombaroccio, Italia</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Situato a Mombaroccio, nelle Marche, l'Amapolas - Villaggio &amp; Camping offre sistemazioni con parcheggio privato gratuito.
+Ogni unità è dotata di aria condizionata, bagno privato e angolo cottura con frigorifero e piano cottura. Per una maggiore comodità, la struttura fornisce asciugamani e lenzuola a un costo aggiuntivo.
+Potrete rilassarvi nel giardino o nell'area salotto in comune.
+Il campeggio dista 36 km da Rimini e 26 km da Riccione. 30 km dall'Aeroporto Internazionale Federico Fellini, lo scalo più vicino.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Un viaggio nel cuore verde delle Marche: l'Amapolas Villaggio è situato tra le dolci colline di Villagrande di Mombaroccio, punto di partenza ideale per vivere i sapori e i colori della nostra terra.
+Da Casa Iris a Casa Dalia, a disposizione dei nostri ospiti casette mobili di diverse dimensioni in cui soggiornare nel comfort più totale: dotate di cucina attrezzata, bagno con doccia, aria condizionata e patio con vista sul paesaggio rurale, gli alloggi sono la soluzione ideale per famiglie, gruppi di amici, cicloturisti pronti a scoprire le bellezze naturali e storiche della regione.
+Assicuriamo ai nostri ospiti un ambiente familiare e tranquillo. Il nostro staff è pronto ad offrire informazioni e proposte di attività per rendere il soggiorno sempre più piacevole.
+Amapolas Villaggio offre un parcheggio gratuito a disposizione e possibilità di pranzo e/o cena presso il vicino agriturismo convenzionato "Il Mimulus". 
+Cambio biancheria su richiesta  a pagamento</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Vasca o doccia, Bagno privato, WC, Asciugacapelli, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, Cabina armadio, | VISTA: Vista giardino, | SPAZI ALL'APERTO: Area picnic, Arredamento da esterni, Zona pranzo all'aperto, Arredamento da esterno, Barbecue, Barbecue
+a pagamento, Patio, Terrazza, Giardino, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Cucina, Forno a microonde, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Presa elettrica vicino al letto, Stendibiancheria, | ANIMALI: | ATTIVITÀ: Trasmissione di eventi sportivi in diretta, Spettacolo/musica dal vivo
+a pagamento, Lezioni di cucina
+a pagamento, Happy hour
+a pagamento, Tour in bicicletta
+a pagamento, Tour a piedi
+a pagamento, Giro dei pub
+a pagamento, Equitazione
+Non sul posto
+a pagamento, Escursioni in bicicletta, Escursionismo
+Non sul posto
+a pagamento, Area giochi, Pesca
+Non sul posto
+a pagamento, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, Canali via cavo, TV, | SERVIZI DI RISTORAZIONE: Caffetteria sul posto, Frutta
+a pagamento, Vino/champagne
+a pagamento, Bar, Ristorante, Minibar, | INTERNET: | PARCHEGGIO: | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, Deposito bagagli
+a pagamento, | INTRATTENIMENTO E SERVIZI PER LE FAMIGLIE: Area giochi all'aperto, Area giochi al coperto, Giochi da tavolo/puzzle, Servizio baby-sitter
+a pagamento, | SERVIZI DI PULIZIA: Servizio lavanderia
+a pagamento, | SERVIZI BUSINESS: Spazi per riunioni/banchetti
+a pagamento, | PROTEZIONE E SICUREZZA: Accesso con chiavi, | SERVIZI GENERALI: Ciotole per animali domestici, Consegna spesa a domicilio
+a pagamento, Minimarket sul posto, Sala comune/zona TV, Aria condizionata, Zanzariera, Riscaldamento, Insonorizzazione, Ingresso indipendente, Possibilità di pranzo al sacco, Disponibilità di camere familiari, Ferro e asse da stiro, Camere non fumatori, Ferro da stiro, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/amapolas-villaggio-amp-camping.it.html</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>amapolas-villaggio-amp-camping</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bungalow Verde Mare</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lungomare Marina Palmense, 63900 Marina Palmense, Italia</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Offering sea views and a seasonal outdoor swimming pool, Bungalow Verde Mare offers accommodation conveniently located in Marina Palmense, within a short distance of Porto San Giorgio Beach.
+The camping offers a seating area with a flat-screen TV and a private bathroom with a hairdryer and bidet.
+A children's playground is also available for guests at Bungalow Verde Mare.
+The nearest airport is Ancona Falconara Airport, 62 km from the accommodation.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Carta igienica, Bidet, Bagno privato, WC, Asciugacapelli, | VISTA: Vista mare, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, Barbecue, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Lavatrice, Frigorifero, | SERVIZI IN CAMERA: Divano letto, Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Happy hour
+a pagamento, Spiaggia, Attrezzatura da tennis
+a pagamento, Intrattenimento serale, Locale notturno/DJ, Staff di animazione, Area giochi, Campo da tennis
+a pagamento, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, | INTERNET: | PARCHEGGIO: | ALTRI SERVIZI: Servizio lavanderia
+a pagamento, Servizio baby-sitter
+a pagamento, | SERVIZI GENERALI: Minimarket sul posto, Ferro e asse da stiro, | PISCINA SCOPERTA: Stagionale, Accessibile a ogni età, Sdraio/lettini, Bar a bordo piscina, Ombrelloni, Scivolo d'acqua, | SERVIZI BENESSERE: Ombrelloni
+a pagamento, Sdraio/lettini, Scivolo d'acqua, | LINGUE PARLATE: Inglese, Italiano, | </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/it/bungalow-verde-mare.it.html</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>bungalow-verde-mare</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Camping Norina</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Via Marina Ardizia 181, 61122 Pesaro, Italia</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ubicato a Pesaro, il Camping Norina vanta un ristorante, un centro fitness e una spiaggia privata, e offre la connessione WiFi gratuita in tutte le aree.
+Tutti gli alloggi sono climatizzati e dotati di TV a schermo piatto e di bagno privato con asciugacapelli.
+Presso il Camping Norina avrete a disposizione delle attrezzature per sport acquatici, il miniclub e un'area giochi per bambini.
+La struttura dista 10 minuti di auto da Pesaro e da Fano e 23 km da Cattolica.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>No camping host description</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, Bagno privato, WC, Doccia, | CAMERA DA LETTO: Armadio o guardaroba, | SPAZI ALL'APERTO: Zona pranzo all'aperto, Arredamento da esterno, | CUCINA: Tavolo da pranzo, Piano cottura, Utensili da cucina, Frigorifero, Angolo cottura, | SERVIZI IN CAMERA: Stendibiancheria, Stand appendiabiti, | ANIMALI: | ATTIVITÀ: Spiaggia, Fronte spiaggia, Attrezzature per sport acquatici sul posto, Spiaggia privata, Area giochi, | AREA SOGGIORNO: Zona pranzo, Divano, Zona soggiorno, | MEDIA E TECNOLOGIA: TV a schermo piatto, TV, | SERVIZI DI RISTORAZIONE: Bar, Ristorante, | INTERNET: | PARCHEGGIO: | SERVIZI GENERALI: Minimarket sul posto, Aria condizionata, Zanzariera, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere non fumatori, | LINGUE PARLATE: Tedesco, Inglese, Francese, Italiano, | </t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.booking.com/hotel/it/camping-spiaggia-di-velluto.it.html</t>
+          <t>https://www.booking.com/hotel/it/camping-norina.it.html</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>camping-spiaggia-di-velluto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Camping Villaggio Cortina</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Lungomare Italia 1/1, 60019 Senigallia, Italia</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Questa struttura si trova a 1 minuto a piedi dalla spiaggia. Il Camping Villaggio Cortina sorge sul lungomare di Senigallia, proprio di fronte alla spiaggia. Offre la connessione Wi-Fi gratuita nella zona della reception.
-Alcune unità sono dotate di aria condizionata, angolo cottura con frigorifero e zona pranzo.
-La struttura dispone di un bar in loco dove potrete gustare un drink. A vostra disposizione anche una spiaggia privata.
-Il Camping Cortina dista 5 km dalla stazione ferroviaria di Senigallia e 24 km da Ancona.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Da più di 15 anni ospitiamo famiglie, coppie e campeggiatori nella nostra struttura. 
-Abbiamo piazzole per tende, roulotte e camper e comode mobilhouse da 4 o 5 posti.
-Il nostro pacchetto all-inclusive vi permette di pagare una sola volta per avere tutto ciò che può servirvi, mobilhouse, parcheggio, pulizie animazione e servizio spiaggia tutto compreso!
-Voi dovrete portare soltando la crema solare!</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAGNO: Asciugamani/lenzuola disponibili a pagamento, | SPAZI ALL'APERTO: Arredamento da esterni, Barbecue, Terrazza, Giardino, | CUCINA: Frigorifero, | SERVIZI IN CAMERA: Stendibiancheria, | ANIMALI: | ATTIVITÀ: Spiaggia, Intrattenimento serale, Fronte spiaggia, Staff di animazione, Spiaggia privata, Windsurf
-Non sul posto
-a pagamento, Ping-pong, | SERVIZI DI RISTORAZIONE: Pasti per bambini
-a pagamento, Snack bar, Bar, Ristorante, | INTERNET: | PARCHEGGIO: Parcheggio per disabili, Parcheggio in strada, | TRASPORTI: Biglietti per i mezzi di trasporto, | ALTRI SERVIZI: Servizio navetta, Servizio lavanderia
-a pagamento, | SERVIZI DI ACCOGLIENZA: Fattura disponibile su richiesta, | PROTEZIONE E SICUREZZA: Estintori, Accesso con chiavi, | SERVIZI GENERALI: Aria condizionata, Riscaldamento, Ingresso indipendente, Disponibilità di camere familiari, Camere/strutture per ospiti disabili, Camere non fumatori, | ACCESSIBILITÀ: Lavabo più basso, WC con maniglioni, Accesso su sedia a rotelle, | SERVIZI BENESSERE: Ombrelloni, | LINGUE PARLATE: Inglese, Italiano, | </t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.booking.com/hotel/it/villaggio-cortina.it.html</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>villaggio-cortina</t>
+          <t>camping-norina</t>
         </is>
       </c>
     </row>
